--- a/data/merged/2026-10-08/MERGED_FR_Mite-Vacuum_2026-10-08.xlsx
+++ b/data/merged/2026-10-08/MERGED_FR_Mite-Vacuum_2026-10-08.xlsx
@@ -5462,13 +5462,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5506,13 +5506,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5638,13 +5638,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5682,13 +5682,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5726,13 +5726,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5770,13 +5770,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5814,13 +5814,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5837,50 +5837,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId42" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="43" name="Product 43">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId43" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6222,7 +6178,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR44"/>
+  <dimension ref="A1:BR43"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -11139,104 +11095,212 @@
       <c r="B24" s="13"/>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>B0DWJQ9GFY</t>
+          <t>B0F6MX5L26</t>
         </is>
       </c>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14" t="inlineStr">
+        <is>
+          <t>JIGOO</t>
+        </is>
+      </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.frundefined</t>
+          <t>https://www.amazon.fr/stores/JIGOO-FR/page/17D55FBF-0728-4B52-B93A-38FB4976CB6E?lp_asin=B0F6MX5L26&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>Hocomay Aspirateur sans fil avec lumière UV-C, aspirateur à main 16 kPa avec écran LED, filtre HEPA, ultrasons, aspirateur de</t>
+          <t>JIGOO S100 Aspirateur de Matelas sans Fil：Aspirateur Anti-Acariens avec UV, 80000 TR/Min pour Nettoyage Profond des Matelas/L</t>
         </is>
       </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0DWJQ9GFY?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0F6MX5L26?psc=1</t>
         </is>
       </c>
       <c r="K24" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61bbwwWUftL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71zSxKlDt9L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>B0DWJQ9GFY</t>
-        </is>
-      </c>
-      <c r="M24" s="14"/>
-      <c r="N24" s="14"/>
-      <c r="O24" s="15"/>
-      <c r="P24" s="15"/>
-      <c r="Q24" s="16"/>
-      <c r="R24" s="17"/>
-      <c r="S24" s="18"/>
+          <t>B0F6MX5L26</t>
+        </is>
+      </c>
+      <c r="M24" s="14" t="inlineStr">
+        <is>
+          <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Aspirateurs:Aspirateurs pour futons</t>
+        </is>
+      </c>
+      <c r="N24" s="14" t="inlineStr">
+        <is>
+          <t>Voir les 100 premiers en Cuisine et Maison</t>
+        </is>
+      </c>
+      <c r="O24" s="15">
+        <v>506948</v>
+      </c>
+      <c r="P24" s="15">
+        <v>-11933</v>
+      </c>
+      <c r="Q24" s="16">
+        <v>-0.02</v>
+      </c>
+      <c r="R24" s="17" t="inlineStr">
+        <is>
+          <t>Aspirateurs pour futons</t>
+        </is>
+      </c>
+      <c r="S24" s="18" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="T24" s="15"/>
       <c r="U24" s="16"/>
       <c r="V24" s="15"/>
       <c r="W24" s="15"/>
       <c r="X24" s="15"/>
-      <c r="Y24" s="19"/>
-      <c r="Z24" s="20"/>
+      <c r="Y24" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z24" s="20">
+        <v>109.99</v>
+      </c>
       <c r="AA24"/>
       <c r="AB24"/>
       <c r="AC24" s="2"/>
       <c r="AD24" s="19">
+        <v>100</v>
+      </c>
+      <c r="AE24" s="15">
         <v>2</v>
       </c>
-      <c r="AE24" s="15"/>
       <c r="AF24" s="21">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="AG24" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH24" s="20"/>
+        <v>1</v>
+      </c>
+      <c r="AH24" s="20">
+        <v>8.03</v>
+      </c>
       <c r="AI24" s="16">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="AJ24"/>
-      <c r="AK24" s="13"/>
-      <c r="AL24" s="19"/>
-      <c r="AM24" s="13"/>
+      <c r="AK24" s="13" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AL24" s="19">
+        <v>483</v>
+      </c>
+      <c r="AM24" s="13" t="inlineStr">
+        <is>
+          <t>FBA</t>
+        </is>
+      </c>
       <c r="AN24" s="13"/>
       <c r="AO24" s="13"/>
       <c r="AP24"/>
-      <c r="AQ24" s="19"/>
-      <c r="AR24" s="19"/>
-      <c r="AS24" s="14"/>
-      <c r="AT24" s="13"/>
-      <c r="AU24" s="13"/>
-      <c r="AV24" s="14"/>
-      <c r="AW24" s="13"/>
+      <c r="AQ24" s="19">
+        <v>7</v>
+      </c>
+      <c r="AR24" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS24" s="14" t="inlineStr">
+        <is>
+          <t>SLACK LGD</t>
+        </is>
+      </c>
+      <c r="AT24" s="13" t="inlineStr">
+        <is>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="AU24" s="13" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="AV24" s="14" t="inlineStr">
+        <is>
+          <t>BARCELONA BARCELONA 08020 ES</t>
+        </is>
+      </c>
+      <c r="AW24" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3UYKG1D6EID1Q</t>
+        </is>
+      </c>
       <c r="AX24" s="13"/>
       <c r="AY24" s="13"/>
       <c r="AZ24" s="13"/>
       <c r="BA24" s="13"/>
       <c r="BB24" s="13"/>
-      <c r="BC24" s="13"/>
+      <c r="BC24" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD24" s="13"/>
       <c r="BE24" s="13"/>
       <c r="BF24" s="13"/>
       <c r="BG24" s="13"/>
       <c r="BH24" s="14"/>
       <c r="BI24" s="23"/>
-      <c r="BJ24" s="23"/>
-      <c r="BK24" s="23"/>
-      <c r="BL24" s="23"/>
-      <c r="BM24" s="23"/>
-      <c r="BN24" s="23"/>
-      <c r="BO24" s="23"/>
-      <c r="BP24" s="23"/>
-      <c r="BQ24" s="23"/>
-      <c r="BR24" s="13"/>
+      <c r="BJ24" s="23" t="inlineStr">
+        <is>
+          <t>1.45 kg</t>
+        </is>
+      </c>
+      <c r="BK24" s="23" t="inlineStr">
+        <is>
+          <t>1.45 kg</t>
+        </is>
+      </c>
+      <c r="BL24" s="23" t="inlineStr">
+        <is>
+          <t>23.5 x 12 x 26 cm</t>
+        </is>
+      </c>
+      <c r="BM24" s="23" t="inlineStr">
+        <is>
+          <t>23.50 x 12.00 x 26.00 cm</t>
+        </is>
+      </c>
+      <c r="BN24" s="23" t="inlineStr">
+        <is>
+          <t>1.44 kg</t>
+        </is>
+      </c>
+      <c r="BO24" s="23" t="inlineStr">
+        <is>
+          <t>1.44 kg</t>
+        </is>
+      </c>
+      <c r="BP24" s="23" t="inlineStr">
+        <is>
+          <t>31.7 x 26 x 19.1 cm</t>
+        </is>
+      </c>
+      <c r="BQ24" s="23" t="inlineStr">
+        <is>
+          <t>31.70 x 26.00 x 19.10 cm</t>
+        </is>
+      </c>
+      <c r="BR24" s="13" t="inlineStr">
+        <is>
+          <t>标准包裹</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13">
@@ -11245,212 +11309,104 @@
       <c r="B25" s="13"/>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>B0F6MX5L26</t>
+          <t>B0F6XNKG8M</t>
         </is>
       </c>
       <c r="D25" s="14"/>
       <c r="E25" s="14"/>
-      <c r="F25" s="14" t="inlineStr">
-        <is>
-          <t>JIGOO</t>
-        </is>
-      </c>
+      <c r="F25" s="14"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/JIGOO-FR/page/17D55FBF-0728-4B52-B93A-38FB4976CB6E?lp_asin=B0F6MX5L26&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.frundefined</t>
         </is>
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>JIGOO S100 Aspirateur de Matelas sans Fil：Aspirateur Anti-Acariens avec UV, 80000 TR/Min pour Nettoyage Profond des Matelas/L</t>
+          <t>Tiazhan Aspirateur Matelas Anti Acariens, Lumière UV-C et 400 WsÉlimine 99,9% | Air Chaud à 60 °C, Filtre HEPA et Dépoussiér</t>
         </is>
       </c>
       <c r="I25" s="14"/>
       <c r="J25" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0F6MX5L26?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0F6XNKG8M?psc=1</t>
         </is>
       </c>
       <c r="K25" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71zSxKlDt9L._AC_US600_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71iADJb-ECL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L25" s="14" t="inlineStr">
         <is>
-          <t>B0F6MX5L26</t>
-        </is>
-      </c>
-      <c r="M25" s="14" t="inlineStr">
-        <is>
-          <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Aspirateurs:Aspirateurs pour futons</t>
-        </is>
-      </c>
-      <c r="N25" s="14" t="inlineStr">
-        <is>
-          <t>Voir les 100 premiers en Cuisine et Maison</t>
-        </is>
-      </c>
-      <c r="O25" s="15">
-        <v>506948</v>
-      </c>
-      <c r="P25" s="15">
-        <v>-11933</v>
-      </c>
-      <c r="Q25" s="16">
-        <v>-0.02</v>
-      </c>
-      <c r="R25" s="17" t="inlineStr">
-        <is>
-          <t>Aspirateurs pour futons</t>
-        </is>
-      </c>
-      <c r="S25" s="18" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+          <t>B0F6XNKG8M</t>
+        </is>
+      </c>
+      <c r="M25" s="14"/>
+      <c r="N25" s="14"/>
+      <c r="O25" s="15"/>
+      <c r="P25" s="15"/>
+      <c r="Q25" s="16"/>
+      <c r="R25" s="17"/>
+      <c r="S25" s="18"/>
       <c r="T25" s="15"/>
       <c r="U25" s="16"/>
       <c r="V25" s="15"/>
       <c r="W25" s="15"/>
       <c r="X25" s="15"/>
-      <c r="Y25" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z25" s="20">
-        <v>109.99</v>
-      </c>
+      <c r="Y25" s="19"/>
+      <c r="Z25" s="20"/>
       <c r="AA25"/>
       <c r="AB25"/>
       <c r="AC25" s="2"/>
       <c r="AD25" s="19">
-        <v>100</v>
-      </c>
-      <c r="AE25" s="15">
-        <v>2</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="AE25" s="15"/>
       <c r="AF25" s="21">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AG25" s="22">
-        <v>1</v>
-      </c>
-      <c r="AH25" s="20">
-        <v>8.03</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH25" s="20"/>
       <c r="AI25" s="16">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="AJ25"/>
-      <c r="AK25" s="13" t="inlineStr">
-        <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AL25" s="19">
-        <v>483</v>
-      </c>
-      <c r="AM25" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
+      <c r="AK25" s="13"/>
+      <c r="AL25" s="19"/>
+      <c r="AM25" s="13"/>
       <c r="AN25" s="13"/>
       <c r="AO25" s="13"/>
       <c r="AP25"/>
-      <c r="AQ25" s="19">
-        <v>7</v>
-      </c>
-      <c r="AR25" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS25" s="14" t="inlineStr">
-        <is>
-          <t>SLACK LGD</t>
-        </is>
-      </c>
-      <c r="AT25" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU25" s="13" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="AV25" s="14" t="inlineStr">
-        <is>
-          <t>BARCELONA BARCELONA 08020 ES</t>
-        </is>
-      </c>
-      <c r="AW25" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3UYKG1D6EID1Q</t>
-        </is>
-      </c>
+      <c r="AQ25" s="19"/>
+      <c r="AR25" s="19"/>
+      <c r="AS25" s="14"/>
+      <c r="AT25" s="13"/>
+      <c r="AU25" s="13"/>
+      <c r="AV25" s="14"/>
+      <c r="AW25" s="13"/>
       <c r="AX25" s="13"/>
       <c r="AY25" s="13"/>
       <c r="AZ25" s="13"/>
       <c r="BA25" s="13"/>
       <c r="BB25" s="13"/>
-      <c r="BC25" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC25" s="13"/>
       <c r="BD25" s="13"/>
       <c r="BE25" s="13"/>
       <c r="BF25" s="13"/>
       <c r="BG25" s="13"/>
       <c r="BH25" s="14"/>
       <c r="BI25" s="23"/>
-      <c r="BJ25" s="23" t="inlineStr">
-        <is>
-          <t>1.45 kg</t>
-        </is>
-      </c>
-      <c r="BK25" s="23" t="inlineStr">
-        <is>
-          <t>1.45 kg</t>
-        </is>
-      </c>
-      <c r="BL25" s="23" t="inlineStr">
-        <is>
-          <t>23.5 x 12 x 26 cm</t>
-        </is>
-      </c>
-      <c r="BM25" s="23" t="inlineStr">
-        <is>
-          <t>23.50 x 12.00 x 26.00 cm</t>
-        </is>
-      </c>
-      <c r="BN25" s="23" t="inlineStr">
-        <is>
-          <t>1.44 kg</t>
-        </is>
-      </c>
-      <c r="BO25" s="23" t="inlineStr">
-        <is>
-          <t>1.44 kg</t>
-        </is>
-      </c>
-      <c r="BP25" s="23" t="inlineStr">
-        <is>
-          <t>31.7 x 26 x 19.1 cm</t>
-        </is>
-      </c>
-      <c r="BQ25" s="23" t="inlineStr">
-        <is>
-          <t>31.70 x 26.00 x 19.10 cm</t>
-        </is>
-      </c>
-      <c r="BR25" s="13" t="inlineStr">
-        <is>
-          <t>标准包裹</t>
-        </is>
-      </c>
+      <c r="BJ25" s="23"/>
+      <c r="BK25" s="23"/>
+      <c r="BL25" s="23"/>
+      <c r="BM25" s="23"/>
+      <c r="BN25" s="23"/>
+      <c r="BO25" s="23"/>
+      <c r="BP25" s="23"/>
+      <c r="BQ25" s="23"/>
+      <c r="BR25" s="13"/>
     </row>
     <row r="26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="13">
@@ -11459,104 +11415,214 @@
       <c r="B26" s="13"/>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>B0F6XNKG8M</t>
+          <t>B0F9NJM4V9</t>
         </is>
       </c>
       <c r="D26" s="14"/>
       <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
+      <c r="F26" s="14" t="inlineStr">
+        <is>
+          <t>Liwankaqi</t>
+        </is>
+      </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.frundefined</t>
+          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Liwankaqi</t>
         </is>
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>Tiazhan Aspirateur Matelas Anti Acariens, Lumière UV-C et 400 WsÉlimine 99,9% | Air Chaud à 60 °C, Filtre HEPA et Dépoussiér</t>
+          <t>Liwankaqi Aspirateur anti-acariens pour matelas, avec UV C et ultrasons, aspiration 8 KPa, sans fil, anti-allergène, pour lit</t>
         </is>
       </c>
       <c r="I26" s="14"/>
       <c r="J26" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0F6XNKG8M?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0F9NJM4V9?psc=1</t>
         </is>
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71iADJb-ECL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61GdOBS8v+L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>B0F6XNKG8M</t>
-        </is>
-      </c>
-      <c r="M26" s="14"/>
-      <c r="N26" s="14"/>
-      <c r="O26" s="15"/>
+          <t>B0F9NJM4V9</t>
+        </is>
+      </c>
+      <c r="M26" s="14" t="inlineStr">
+        <is>
+          <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Aspirateurs:Aspirateurs pour futons</t>
+        </is>
+      </c>
+      <c r="N26" s="14" t="inlineStr">
+        <is>
+          <t>Voir les 100 premiers en Cuisine et Maison</t>
+        </is>
+      </c>
+      <c r="O26" s="15">
+        <v>2403769</v>
+      </c>
       <c r="P26" s="15"/>
-      <c r="Q26" s="16"/>
-      <c r="R26" s="17"/>
-      <c r="S26" s="18"/>
+      <c r="Q26" s="16">
+        <v>0</v>
+      </c>
+      <c r="R26" s="17" t="inlineStr">
+        <is>
+          <t>Aspirateurs pour futons</t>
+        </is>
+      </c>
+      <c r="S26" s="18" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
       <c r="T26" s="15"/>
       <c r="U26" s="16"/>
       <c r="V26" s="15"/>
       <c r="W26" s="15"/>
       <c r="X26" s="15"/>
-      <c r="Y26" s="19"/>
-      <c r="Z26" s="20"/>
+      <c r="Y26" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z26" s="20">
+        <v>48.22</v>
+      </c>
       <c r="AA26"/>
       <c r="AB26"/>
       <c r="AC26" s="2"/>
       <c r="AD26" s="19">
-        <v>10</v>
-      </c>
-      <c r="AE26" s="15"/>
+        <v>2</v>
+      </c>
+      <c r="AE26" s="15">
+        <v>0</v>
+      </c>
       <c r="AF26" s="21">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="AG26" s="22">
         <v>0</v>
       </c>
-      <c r="AH26" s="20"/>
+      <c r="AH26" s="20">
+        <v>8.44</v>
+      </c>
       <c r="AI26" s="16">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="AJ26"/>
-      <c r="AK26" s="13"/>
-      <c r="AL26" s="19"/>
-      <c r="AM26" s="13"/>
+      <c r="AK26" s="13" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AL26" s="19">
+        <v>405</v>
+      </c>
+      <c r="AM26" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="AN26" s="13"/>
       <c r="AO26" s="13"/>
       <c r="AP26"/>
-      <c r="AQ26" s="19"/>
-      <c r="AR26" s="19"/>
-      <c r="AS26" s="14"/>
-      <c r="AT26" s="13"/>
-      <c r="AU26" s="13"/>
-      <c r="AV26" s="14"/>
-      <c r="AW26" s="13"/>
+      <c r="AQ26" s="19">
+        <v>8</v>
+      </c>
+      <c r="AR26" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS26" s="14" t="inlineStr">
+        <is>
+          <t>liwantech</t>
+        </is>
+      </c>
+      <c r="AT26" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU26" s="13" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV26" s="14" t="inlineStr">
+        <is>
+          <t>深圳市 南山区 广东 518000 CN</t>
+        </is>
+      </c>
+      <c r="AW26" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1CO438NU9H9Y</t>
+        </is>
+      </c>
       <c r="AX26" s="13"/>
       <c r="AY26" s="13"/>
       <c r="AZ26" s="13"/>
       <c r="BA26" s="13"/>
       <c r="BB26" s="13"/>
-      <c r="BC26" s="13"/>
-      <c r="BD26" s="13"/>
+      <c r="BC26" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD26" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE26" s="13"/>
       <c r="BF26" s="13"/>
       <c r="BG26" s="13"/>
       <c r="BH26" s="14"/>
       <c r="BI26" s="23"/>
-      <c r="BJ26" s="23"/>
-      <c r="BK26" s="23"/>
-      <c r="BL26" s="23"/>
-      <c r="BM26" s="23"/>
-      <c r="BN26" s="23"/>
-      <c r="BO26" s="23"/>
-      <c r="BP26" s="23"/>
-      <c r="BQ26" s="23"/>
-      <c r="BR26" s="13"/>
+      <c r="BJ26" s="23" t="inlineStr">
+        <is>
+          <t>2.24 kg</t>
+        </is>
+      </c>
+      <c r="BK26" s="23" t="inlineStr">
+        <is>
+          <t>2.24 kg</t>
+        </is>
+      </c>
+      <c r="BL26" s="23" t="inlineStr">
+        <is>
+          <t>29.4 x 2.7 x 18.5 cm</t>
+        </is>
+      </c>
+      <c r="BM26" s="23" t="inlineStr">
+        <is>
+          <t>29.40 x 2.70 x 18.50 cm</t>
+        </is>
+      </c>
+      <c r="BN26" s="23" t="inlineStr">
+        <is>
+          <t>2.24 kg</t>
+        </is>
+      </c>
+      <c r="BO26" s="23" t="inlineStr">
+        <is>
+          <t>2.24 kg</t>
+        </is>
+      </c>
+      <c r="BP26" s="23" t="inlineStr">
+        <is>
+          <t>34 x 31 x 23 cm</t>
+        </is>
+      </c>
+      <c r="BQ26" s="23" t="inlineStr">
+        <is>
+          <t>34.00 x 31.00 x 23.00 cm</t>
+        </is>
+      </c>
+      <c r="BR26" s="13" t="inlineStr">
+        <is>
+          <t>标准包裹</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="13">
@@ -11565,40 +11631,40 @@
       <c r="B27" s="13"/>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>B0F9NJM4V9</t>
+          <t>B0FDWVV95V</t>
         </is>
       </c>
       <c r="D27" s="14"/>
       <c r="E27" s="14"/>
       <c r="F27" s="14" t="inlineStr">
         <is>
-          <t>Liwankaqi</t>
+          <t>JIGOO</t>
         </is>
       </c>
       <c r="G27" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Liwankaqi</t>
+          <t>https://www.amazon.fr/stores/JIGOO-FR/page/17D55FBF-0728-4B52-B93A-38FB4976CB6E?lp_asin=B0FDWVV95V&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>Liwankaqi Aspirateur anti-acariens pour matelas, avec UV C et ultrasons, aspiration 8 KPa, sans fil, anti-allergène, pour lit</t>
+          <t>JIGOO T600 Aspirateur anti-acariens/Floral Delight (huile essentielle végétale)</t>
         </is>
       </c>
       <c r="I27" s="14"/>
       <c r="J27" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0F9NJM4V9?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0FDWVV95V?psc=1</t>
         </is>
       </c>
       <c r="K27" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61GdOBS8v+L._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61tL+-AcL6L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L27" s="14" t="inlineStr">
         <is>
-          <t>B0F9NJM4V9</t>
+          <t>B0FDWVV95V</t>
         </is>
       </c>
       <c r="M27" s="14" t="inlineStr">
@@ -11612,9 +11678,11 @@
         </is>
       </c>
       <c r="O27" s="15">
-        <v>2403769</v>
-      </c>
-      <c r="P27" s="15"/>
+        <v>1529233</v>
+      </c>
+      <c r="P27" s="15">
+        <v>-4301</v>
+      </c>
       <c r="Q27" s="16">
         <v>0</v>
       </c>
@@ -11625,7 +11693,7 @@
       </c>
       <c r="S27" s="18" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="T27" s="15"/>
@@ -11637,37 +11705,37 @@
         <v>1</v>
       </c>
       <c r="Z27" s="20">
-        <v>48.22</v>
+        <v>18.99</v>
       </c>
       <c r="AA27"/>
       <c r="AB27"/>
       <c r="AC27" s="2"/>
       <c r="AD27" s="19">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AE27" s="15">
         <v>0</v>
       </c>
       <c r="AF27" s="21">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="AG27" s="22">
         <v>0</v>
       </c>
       <c r="AH27" s="20">
-        <v>8.44</v>
+        <v>2.4</v>
       </c>
       <c r="AI27" s="16">
-        <v>0.68</v>
+        <v>0.72</v>
       </c>
       <c r="AJ27"/>
       <c r="AK27" s="13" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AL27" s="19">
-        <v>405</v>
+        <v>422</v>
       </c>
       <c r="AM27" s="13" t="inlineStr">
         <is>
@@ -11677,15 +11745,13 @@
       <c r="AN27" s="13"/>
       <c r="AO27" s="13"/>
       <c r="AP27"/>
-      <c r="AQ27" s="19">
-        <v>8</v>
-      </c>
+      <c r="AQ27" s="19"/>
       <c r="AR27" s="19">
         <v>1</v>
       </c>
       <c r="AS27" s="14" t="inlineStr">
         <is>
-          <t>liwantech</t>
+          <t>yefengdianzi</t>
         </is>
       </c>
       <c r="AT27" s="13" t="inlineStr">
@@ -11695,17 +11761,17 @@
       </c>
       <c r="AU27" s="13" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CN(HK)</t>
         </is>
       </c>
       <c r="AV27" s="14" t="inlineStr">
         <is>
-          <t>深圳市 南山区 广东 518000 CN</t>
+          <t>KWUN TONG HONG KONG 999077 HK</t>
         </is>
       </c>
       <c r="AW27" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1CO438NU9H9Y</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1OG68CATOOAOD</t>
         </is>
       </c>
       <c r="AX27" s="13"/>
@@ -11713,16 +11779,8 @@
       <c r="AZ27" s="13"/>
       <c r="BA27" s="13"/>
       <c r="BB27" s="13"/>
-      <c r="BC27" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD27" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC27" s="13"/>
+      <c r="BD27" s="13"/>
       <c r="BE27" s="13"/>
       <c r="BF27" s="13"/>
       <c r="BG27" s="13"/>
@@ -11730,47 +11788,43 @@
       <c r="BI27" s="23"/>
       <c r="BJ27" s="23" t="inlineStr">
         <is>
-          <t>2.24 kg</t>
+          <t>50 g</t>
         </is>
       </c>
       <c r="BK27" s="23" t="inlineStr">
         <is>
-          <t>2.24 kg</t>
+          <t>50.00 g</t>
         </is>
       </c>
       <c r="BL27" s="23" t="inlineStr">
         <is>
-          <t>29.4 x 2.7 x 18.5 cm</t>
-        </is>
-      </c>
-      <c r="BM27" s="23" t="inlineStr">
-        <is>
-          <t>29.40 x 2.70 x 18.50 cm</t>
-        </is>
-      </c>
+          <t>6L x 1,3l x 8H centimètres</t>
+        </is>
+      </c>
+      <c r="BM27" s="23"/>
       <c r="BN27" s="23" t="inlineStr">
         <is>
-          <t>2.24 kg</t>
+          <t>50 g</t>
         </is>
       </c>
       <c r="BO27" s="23" t="inlineStr">
         <is>
-          <t>2.24 kg</t>
+          <t>50.00 g</t>
         </is>
       </c>
       <c r="BP27" s="23" t="inlineStr">
         <is>
-          <t>34 x 31 x 23 cm</t>
+          <t>10 x 6 x 1.5 cm</t>
         </is>
       </c>
       <c r="BQ27" s="23" t="inlineStr">
         <is>
-          <t>34.00 x 31.00 x 23.00 cm</t>
+          <t>10.00 x 6.00 x 1.50 cm</t>
         </is>
       </c>
       <c r="BR27" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型信封</t>
         </is>
       </c>
     </row>
@@ -11781,149 +11835,83 @@
       <c r="B28" s="13"/>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>B0FDWVV95V</t>
+          <t>B0FN3V6RFQ</t>
         </is>
       </c>
       <c r="D28" s="14"/>
       <c r="E28" s="14"/>
-      <c r="F28" s="14" t="inlineStr">
-        <is>
-          <t>JIGOO</t>
-        </is>
-      </c>
+      <c r="F28" s="14"/>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/JIGOO-FR/page/17D55FBF-0728-4B52-B93A-38FB4976CB6E?lp_asin=B0FDWVV95V&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.frundefined</t>
         </is>
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>JIGOO T600 Aspirateur anti-acariens/Floral Delight (huile essentielle végétale)</t>
+          <t>Minthouz Aspirateur Anti-acariens</t>
         </is>
       </c>
       <c r="I28" s="14"/>
       <c r="J28" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0FDWVV95V?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0FN3V6RFQ?psc=1</t>
         </is>
       </c>
       <c r="K28" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61tL+-AcL6L._AC_US600_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71YynWtKuIL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>B0FDWVV95V</t>
-        </is>
-      </c>
-      <c r="M28" s="14" t="inlineStr">
-        <is>
-          <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Aspirateurs:Aspirateurs pour futons</t>
-        </is>
-      </c>
-      <c r="N28" s="14" t="inlineStr">
-        <is>
-          <t>Voir les 100 premiers en Cuisine et Maison</t>
-        </is>
-      </c>
-      <c r="O28" s="15">
-        <v>1529233</v>
-      </c>
-      <c r="P28" s="15">
-        <v>-4301</v>
-      </c>
-      <c r="Q28" s="16">
-        <v>0</v>
-      </c>
-      <c r="R28" s="17" t="inlineStr">
-        <is>
-          <t>Aspirateurs pour futons</t>
-        </is>
-      </c>
-      <c r="S28" s="18" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
+          <t>B0FN3V6RFQ</t>
+        </is>
+      </c>
+      <c r="M28" s="14"/>
+      <c r="N28" s="14"/>
+      <c r="O28" s="15"/>
+      <c r="P28" s="15"/>
+      <c r="Q28" s="16"/>
+      <c r="R28" s="17"/>
+      <c r="S28" s="18"/>
       <c r="T28" s="15"/>
       <c r="U28" s="16"/>
       <c r="V28" s="15"/>
       <c r="W28" s="15"/>
       <c r="X28" s="15"/>
-      <c r="Y28" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z28" s="20">
-        <v>18.99</v>
-      </c>
+      <c r="Y28" s="19"/>
+      <c r="Z28" s="20"/>
       <c r="AA28"/>
       <c r="AB28"/>
       <c r="AC28" s="2"/>
       <c r="AD28" s="19">
-        <v>10</v>
-      </c>
-      <c r="AE28" s="15">
-        <v>0</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="AE28" s="15"/>
       <c r="AF28" s="21">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AG28" s="22">
         <v>0</v>
       </c>
-      <c r="AH28" s="20">
-        <v>2.4</v>
-      </c>
+      <c r="AH28" s="20"/>
       <c r="AI28" s="16">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="AJ28"/>
-      <c r="AK28" s="13" t="inlineStr">
-        <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AL28" s="19">
-        <v>422</v>
-      </c>
-      <c r="AM28" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="AK28" s="13"/>
+      <c r="AL28" s="19"/>
+      <c r="AM28" s="13"/>
       <c r="AN28" s="13"/>
       <c r="AO28" s="13"/>
       <c r="AP28"/>
       <c r="AQ28" s="19"/>
-      <c r="AR28" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS28" s="14" t="inlineStr">
-        <is>
-          <t>yefengdianzi</t>
-        </is>
-      </c>
-      <c r="AT28" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU28" s="13" t="inlineStr">
-        <is>
-          <t>CN(HK)</t>
-        </is>
-      </c>
-      <c r="AV28" s="14" t="inlineStr">
-        <is>
-          <t>KWUN TONG HONG KONG 999077 HK</t>
-        </is>
-      </c>
-      <c r="AW28" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1OG68CATOOAOD</t>
-        </is>
-      </c>
+      <c r="AR28" s="19"/>
+      <c r="AS28" s="14"/>
+      <c r="AT28" s="13"/>
+      <c r="AU28" s="13"/>
+      <c r="AV28" s="14"/>
+      <c r="AW28" s="13"/>
       <c r="AX28" s="13"/>
       <c r="AY28" s="13"/>
       <c r="AZ28" s="13"/>
@@ -11936,47 +11924,15 @@
       <c r="BG28" s="13"/>
       <c r="BH28" s="14"/>
       <c r="BI28" s="23"/>
-      <c r="BJ28" s="23" t="inlineStr">
-        <is>
-          <t>50 g</t>
-        </is>
-      </c>
-      <c r="BK28" s="23" t="inlineStr">
-        <is>
-          <t>50.00 g</t>
-        </is>
-      </c>
-      <c r="BL28" s="23" t="inlineStr">
-        <is>
-          <t>6L x 1,3l x 8H centimètres</t>
-        </is>
-      </c>
+      <c r="BJ28" s="23"/>
+      <c r="BK28" s="23"/>
+      <c r="BL28" s="23"/>
       <c r="BM28" s="23"/>
-      <c r="BN28" s="23" t="inlineStr">
-        <is>
-          <t>50 g</t>
-        </is>
-      </c>
-      <c r="BO28" s="23" t="inlineStr">
-        <is>
-          <t>50.00 g</t>
-        </is>
-      </c>
-      <c r="BP28" s="23" t="inlineStr">
-        <is>
-          <t>10 x 6 x 1.5 cm</t>
-        </is>
-      </c>
-      <c r="BQ28" s="23" t="inlineStr">
-        <is>
-          <t>10.00 x 6.00 x 1.50 cm</t>
-        </is>
-      </c>
-      <c r="BR28" s="13" t="inlineStr">
-        <is>
-          <t>轻型信封</t>
-        </is>
-      </c>
+      <c r="BN28" s="23"/>
+      <c r="BO28" s="23"/>
+      <c r="BP28" s="23"/>
+      <c r="BQ28" s="23"/>
+      <c r="BR28" s="13"/>
     </row>
     <row r="29" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="13">
@@ -11985,61 +11941,93 @@
       <c r="B29" s="13"/>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>B0FN3V6RFQ</t>
+          <t>B0FVS559GZ</t>
         </is>
       </c>
       <c r="D29" s="14"/>
       <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>Yaasier</t>
+        </is>
+      </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.frundefined</t>
+          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier</t>
         </is>
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>Minthouz Aspirateur Anti-acariens</t>
+          <t>Yaasier Aspirateur Matelas, Aspirateur Anti-acariens pour Matelas avec lumière UV, Aspirateur à Main avec Filtre Hepa, Elimin</t>
         </is>
       </c>
       <c r="I29" s="14"/>
       <c r="J29" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0FN3V6RFQ?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0FVS559GZ?psc=1</t>
         </is>
       </c>
       <c r="K29" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71YynWtKuIL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/31eLjeocEiL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L29" s="14" t="inlineStr">
         <is>
-          <t>B0FN3V6RFQ</t>
-        </is>
-      </c>
-      <c r="M29" s="14"/>
-      <c r="N29" s="14"/>
-      <c r="O29" s="15"/>
+          <t>B0FVS559GZ</t>
+        </is>
+      </c>
+      <c r="M29" s="14" t="inlineStr">
+        <is>
+          <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Aspirateurs:Aspirateurs pour futons</t>
+        </is>
+      </c>
+      <c r="N29" s="14" t="inlineStr">
+        <is>
+          <t>Voir les 100 premiers en Cuisine et Maison</t>
+        </is>
+      </c>
+      <c r="O29" s="15">
+        <v>464846</v>
+      </c>
       <c r="P29" s="15"/>
-      <c r="Q29" s="16"/>
-      <c r="R29" s="17"/>
-      <c r="S29" s="18"/>
+      <c r="Q29" s="16">
+        <v>0</v>
+      </c>
+      <c r="R29" s="17" t="inlineStr">
+        <is>
+          <t>Aspirateurs pour futons
+Aspirateurs à main</t>
+        </is>
+      </c>
+      <c r="S29" s="18" t="inlineStr">
+        <is>
+          <t>16
+84</t>
+        </is>
+      </c>
       <c r="T29" s="15"/>
       <c r="U29" s="16"/>
       <c r="V29" s="15"/>
       <c r="W29" s="15"/>
       <c r="X29" s="15"/>
-      <c r="Y29" s="19"/>
-      <c r="Z29" s="20"/>
+      <c r="Y29" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z29" s="20">
+        <v>21.59</v>
+      </c>
       <c r="AA29"/>
       <c r="AB29"/>
       <c r="AC29" s="2"/>
       <c r="AD29" s="19">
-        <v>35</v>
-      </c>
-      <c r="AE29" s="15"/>
+        <v>28</v>
+      </c>
+      <c r="AE29" s="15">
+        <v>0</v>
+      </c>
       <c r="AF29" s="21">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="AG29" s="22">
         <v>0</v>
@@ -12049,34 +12037,74 @@
         <v>0</v>
       </c>
       <c r="AJ29"/>
-      <c r="AK29" s="13"/>
-      <c r="AL29" s="19"/>
-      <c r="AM29" s="13"/>
+      <c r="AK29" s="13" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AL29" s="19">
+        <v>343</v>
+      </c>
+      <c r="AM29" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="AN29" s="13"/>
       <c r="AO29" s="13"/>
       <c r="AP29"/>
       <c r="AQ29" s="19"/>
-      <c r="AR29" s="19"/>
-      <c r="AS29" s="14"/>
-      <c r="AT29" s="13"/>
+      <c r="AR29" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS29" s="14" t="inlineStr">
+        <is>
+          <t>Renyu</t>
+        </is>
+      </c>
+      <c r="AT29" s="13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="AU29" s="13"/>
       <c r="AV29" s="14"/>
-      <c r="AW29" s="13"/>
+      <c r="AW29" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX</t>
+        </is>
+      </c>
       <c r="AX29" s="13"/>
       <c r="AY29" s="13"/>
       <c r="AZ29" s="13"/>
       <c r="BA29" s="13"/>
       <c r="BB29" s="13"/>
-      <c r="BC29" s="13"/>
+      <c r="BC29" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD29" s="13"/>
       <c r="BE29" s="13"/>
       <c r="BF29" s="13"/>
       <c r="BG29" s="13"/>
       <c r="BH29" s="14"/>
       <c r="BI29" s="23"/>
-      <c r="BJ29" s="23"/>
-      <c r="BK29" s="23"/>
-      <c r="BL29" s="23"/>
+      <c r="BJ29" s="23" t="inlineStr">
+        <is>
+          <t>250 g</t>
+        </is>
+      </c>
+      <c r="BK29" s="23" t="inlineStr">
+        <is>
+          <t>250.00 g</t>
+        </is>
+      </c>
+      <c r="BL29" s="23" t="inlineStr">
+        <is>
+          <t>6L x 4l x 8H centimètres</t>
+        </is>
+      </c>
       <c r="BM29" s="23"/>
       <c r="BN29" s="23"/>
       <c r="BO29" s="23"/>
@@ -12091,93 +12119,61 @@
       <c r="B30" s="13"/>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>B0FVS559GZ</t>
+          <t>B0FYM1D13D</t>
         </is>
       </c>
       <c r="D30" s="14"/>
       <c r="E30" s="14"/>
-      <c r="F30" s="14" t="inlineStr">
-        <is>
-          <t>Yaasier</t>
-        </is>
-      </c>
+      <c r="F30" s="14"/>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier</t>
+          <t>https://www.amazon.frundefined</t>
         </is>
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>Yaasier Aspirateur Matelas, Aspirateur Anti-acariens pour Matelas avec lumière UV, Aspirateur à Main avec Filtre Hepa, Elimin</t>
+          <t>Aspirateur Matelas, Aspirateur Anti-acariens pour Matelas avec lumière UV, Aspirateur à Main avec Filtre Hepa, Elimine 99,99%</t>
         </is>
       </c>
       <c r="I30" s="14"/>
       <c r="J30" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0FVS559GZ?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0FYM1D13D?psc=1</t>
         </is>
       </c>
       <c r="K30" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31eLjeocEiL._AC_US600_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>B0FVS559GZ</t>
-        </is>
-      </c>
-      <c r="M30" s="14" t="inlineStr">
-        <is>
-          <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Aspirateurs:Aspirateurs pour futons</t>
-        </is>
-      </c>
-      <c r="N30" s="14" t="inlineStr">
-        <is>
-          <t>Voir les 100 premiers en Cuisine et Maison</t>
-        </is>
-      </c>
-      <c r="O30" s="15">
-        <v>464846</v>
-      </c>
+          <t>B0FYM1D13D</t>
+        </is>
+      </c>
+      <c r="M30" s="14"/>
+      <c r="N30" s="14"/>
+      <c r="O30" s="15"/>
       <c r="P30" s="15"/>
-      <c r="Q30" s="16">
-        <v>0</v>
-      </c>
-      <c r="R30" s="17" t="inlineStr">
-        <is>
-          <t>Aspirateurs pour futons
-Aspirateurs à main</t>
-        </is>
-      </c>
-      <c r="S30" s="18" t="inlineStr">
-        <is>
-          <t>16
-84</t>
-        </is>
-      </c>
+      <c r="Q30" s="16"/>
+      <c r="R30" s="17"/>
+      <c r="S30" s="18"/>
       <c r="T30" s="15"/>
       <c r="U30" s="16"/>
       <c r="V30" s="15"/>
       <c r="W30" s="15"/>
       <c r="X30" s="15"/>
-      <c r="Y30" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z30" s="20">
-        <v>21.59</v>
-      </c>
+      <c r="Y30" s="19"/>
+      <c r="Z30" s="20"/>
       <c r="AA30"/>
       <c r="AB30"/>
       <c r="AC30" s="2"/>
       <c r="AD30" s="19">
-        <v>28</v>
-      </c>
-      <c r="AE30" s="15">
-        <v>0</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="AE30" s="15"/>
       <c r="AF30" s="21">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AG30" s="22">
         <v>0</v>
@@ -12187,74 +12183,34 @@
         <v>0</v>
       </c>
       <c r="AJ30"/>
-      <c r="AK30" s="13" t="inlineStr">
-        <is>
-          <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AL30" s="19">
-        <v>343</v>
-      </c>
-      <c r="AM30" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="AK30" s="13"/>
+      <c r="AL30" s="19"/>
+      <c r="AM30" s="13"/>
       <c r="AN30" s="13"/>
       <c r="AO30" s="13"/>
       <c r="AP30"/>
       <c r="AQ30" s="19"/>
-      <c r="AR30" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS30" s="14" t="inlineStr">
-        <is>
-          <t>Renyu</t>
-        </is>
-      </c>
-      <c r="AT30" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="AR30" s="19"/>
+      <c r="AS30" s="14"/>
+      <c r="AT30" s="13"/>
       <c r="AU30" s="13"/>
       <c r="AV30" s="14"/>
-      <c r="AW30" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX</t>
-        </is>
-      </c>
+      <c r="AW30" s="13"/>
       <c r="AX30" s="13"/>
       <c r="AY30" s="13"/>
       <c r="AZ30" s="13"/>
       <c r="BA30" s="13"/>
       <c r="BB30" s="13"/>
-      <c r="BC30" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC30" s="13"/>
       <c r="BD30" s="13"/>
       <c r="BE30" s="13"/>
       <c r="BF30" s="13"/>
       <c r="BG30" s="13"/>
       <c r="BH30" s="14"/>
       <c r="BI30" s="23"/>
-      <c r="BJ30" s="23" t="inlineStr">
-        <is>
-          <t>250 g</t>
-        </is>
-      </c>
-      <c r="BK30" s="23" t="inlineStr">
-        <is>
-          <t>250.00 g</t>
-        </is>
-      </c>
-      <c r="BL30" s="23" t="inlineStr">
-        <is>
-          <t>6L x 4l x 8H centimètres</t>
-        </is>
-      </c>
+      <c r="BJ30" s="23"/>
+      <c r="BK30" s="23"/>
+      <c r="BL30" s="23"/>
       <c r="BM30" s="23"/>
       <c r="BN30" s="23"/>
       <c r="BO30" s="23"/>
@@ -12269,61 +12225,91 @@
       <c r="B31" s="13"/>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>B0FYM1D13D</t>
+          <t>B0G4RSJQVT</t>
         </is>
       </c>
       <c r="D31" s="14"/>
       <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
+      <c r="F31" s="14" t="inlineStr">
+        <is>
+          <t>Lubluelu</t>
+        </is>
+      </c>
       <c r="G31" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.frundefined</t>
+          <t>https://www.amazon.fr/stores/Lubluelu/page/C74A1C3B-E92E-40F7-8500-E72C2F4BD6F3?lp_asin=B0G4RSJQVT&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
-          <t>Aspirateur Matelas, Aspirateur Anti-acariens pour Matelas avec lumière UV, Aspirateur à Main avec Filtre Hepa, Elimine 99,99%</t>
+          <t>Lubluelu Aspirateur Anti-Acariens pour Matelas 3 en 1, 18 kPa Puissance d’Aspiration, Élimine 99% des Acariens et Allergènes,</t>
         </is>
       </c>
       <c r="I31" s="14"/>
       <c r="J31" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0FYM1D13D?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0G4RSJQVT?psc=1</t>
         </is>
       </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41T59G+lWKL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L31" s="14" t="inlineStr">
         <is>
-          <t>B0FYM1D13D</t>
-        </is>
-      </c>
-      <c r="M31" s="14"/>
-      <c r="N31" s="14"/>
-      <c r="O31" s="15"/>
+          <t>B0G4RSJQVT</t>
+        </is>
+      </c>
+      <c r="M31" s="14" t="inlineStr">
+        <is>
+          <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Aspirateurs:Aspirateurs pour futons</t>
+        </is>
+      </c>
+      <c r="N31" s="14" t="inlineStr">
+        <is>
+          <t>Voir les 100 premiers en Cuisine et Maison</t>
+        </is>
+      </c>
+      <c r="O31" s="15">
+        <v>703743</v>
+      </c>
       <c r="P31" s="15"/>
-      <c r="Q31" s="16"/>
-      <c r="R31" s="17"/>
-      <c r="S31" s="18"/>
+      <c r="Q31" s="16">
+        <v>0</v>
+      </c>
+      <c r="R31" s="17" t="inlineStr">
+        <is>
+          <t>Aspirateurs pour futons</t>
+        </is>
+      </c>
+      <c r="S31" s="18" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="T31" s="15"/>
       <c r="U31" s="16"/>
       <c r="V31" s="15"/>
       <c r="W31" s="15"/>
       <c r="X31" s="15"/>
-      <c r="Y31" s="19"/>
-      <c r="Z31" s="20"/>
+      <c r="Y31" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z31" s="20">
+        <v>99.99</v>
+      </c>
       <c r="AA31"/>
       <c r="AB31"/>
       <c r="AC31" s="2"/>
       <c r="AD31" s="19">
-        <v>4</v>
-      </c>
-      <c r="AE31" s="15"/>
+        <v>26</v>
+      </c>
+      <c r="AE31" s="15">
+        <v>-39</v>
+      </c>
       <c r="AF31" s="21">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="AG31" s="22">
         <v>0</v>
@@ -12333,34 +12319,74 @@
         <v>0</v>
       </c>
       <c r="AJ31"/>
-      <c r="AK31" s="13"/>
-      <c r="AL31" s="19"/>
-      <c r="AM31" s="13"/>
+      <c r="AK31" s="13" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AL31" s="19">
+        <v>303</v>
+      </c>
+      <c r="AM31" s="13" t="inlineStr">
+        <is>
+          <t>FBA</t>
+        </is>
+      </c>
       <c r="AN31" s="13"/>
       <c r="AO31" s="13"/>
       <c r="AP31"/>
       <c r="AQ31" s="19"/>
-      <c r="AR31" s="19"/>
-      <c r="AS31" s="14"/>
-      <c r="AT31" s="13"/>
+      <c r="AR31" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS31" s="14" t="inlineStr">
+        <is>
+          <t>Lubluelu Official</t>
+        </is>
+      </c>
+      <c r="AT31" s="13" t="inlineStr">
+        <is>
+          <t>FBA</t>
+        </is>
+      </c>
       <c r="AU31" s="13"/>
       <c r="AV31" s="14"/>
-      <c r="AW31" s="13"/>
+      <c r="AW31" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A23BRZJD26C30N</t>
+        </is>
+      </c>
       <c r="AX31" s="13"/>
       <c r="AY31" s="13"/>
       <c r="AZ31" s="13"/>
       <c r="BA31" s="13"/>
       <c r="BB31" s="13"/>
-      <c r="BC31" s="13"/>
+      <c r="BC31" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD31" s="13"/>
       <c r="BE31" s="13"/>
       <c r="BF31" s="13"/>
       <c r="BG31" s="13"/>
       <c r="BH31" s="14"/>
       <c r="BI31" s="23"/>
-      <c r="BJ31" s="23"/>
-      <c r="BK31" s="23"/>
-      <c r="BL31" s="23"/>
+      <c r="BJ31" s="23" t="inlineStr">
+        <is>
+          <t>2,33 Kilograms</t>
+        </is>
+      </c>
+      <c r="BK31" s="23" t="inlineStr">
+        <is>
+          <t>2.33 kg</t>
+        </is>
+      </c>
+      <c r="BL31" s="23" t="inlineStr">
+        <is>
+          <t>30L x 24,5l x 23H centimètres</t>
+        </is>
+      </c>
       <c r="BM31" s="23"/>
       <c r="BN31" s="23"/>
       <c r="BO31" s="23"/>
@@ -12375,40 +12401,40 @@
       <c r="B32" s="13"/>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>B0G4RSJQVT</t>
+          <t>B0GF7CNTYL</t>
         </is>
       </c>
       <c r="D32" s="14"/>
       <c r="E32" s="14"/>
       <c r="F32" s="14" t="inlineStr">
         <is>
-          <t>Lubluelu</t>
+          <t>Liwankaqi</t>
         </is>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/Lubluelu/page/C74A1C3B-E92E-40F7-8500-E72C2F4BD6F3?lp_asin=B0G4RSJQVT&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Liwankaqi</t>
         </is>
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>Lubluelu Aspirateur Anti-Acariens pour Matelas 3 en 1, 18 kPa Puissance d’Aspiration, Élimine 99% des Acariens et Allergènes,</t>
+          <t>Aspirateur de Matelas UV-C Ultrasonique pour Lit et CanapésAspirateur sans fil pour housses de couette, matelas, canapés en</t>
         </is>
       </c>
       <c r="I32" s="14"/>
       <c r="J32" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0G4RSJQVT?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GF7CNTYL?psc=1</t>
         </is>
       </c>
       <c r="K32" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41T59G+lWKL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71H9bRmoUnL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>B0G4RSJQVT</t>
+          <t>B0GF7CNTYL</t>
         </is>
       </c>
       <c r="M32" s="14" t="inlineStr">
@@ -12422,7 +12448,7 @@
         </is>
       </c>
       <c r="O32" s="15">
-        <v>703743</v>
+        <v>1833198</v>
       </c>
       <c r="P32" s="15"/>
       <c r="Q32" s="16">
@@ -12435,7 +12461,7 @@
       </c>
       <c r="S32" s="18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>36</t>
         </is>
       </c>
       <c r="T32" s="15"/>
@@ -12447,35 +12473,35 @@
         <v>1</v>
       </c>
       <c r="Z32" s="20">
-        <v>99.99</v>
+        <v>49.99</v>
       </c>
       <c r="AA32"/>
       <c r="AB32"/>
       <c r="AC32" s="2"/>
       <c r="AD32" s="19">
-        <v>26</v>
-      </c>
-      <c r="AE32" s="15">
-        <v>-39</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AE32" s="15"/>
       <c r="AF32" s="21">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="AG32" s="22">
         <v>0</v>
       </c>
-      <c r="AH32" s="20"/>
+      <c r="AH32" s="20">
+        <v>7.29</v>
+      </c>
       <c r="AI32" s="16">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="AJ32"/>
       <c r="AK32" s="13" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="AL32" s="19">
-        <v>303</v>
+        <v>178</v>
       </c>
       <c r="AM32" s="13" t="inlineStr">
         <is>
@@ -12491,7 +12517,7 @@
       </c>
       <c r="AS32" s="14" t="inlineStr">
         <is>
-          <t>Lubluelu Official</t>
+          <t>liwantech</t>
         </is>
       </c>
       <c r="AT32" s="13" t="inlineStr">
@@ -12499,11 +12525,19 @@
           <t>FBA</t>
         </is>
       </c>
-      <c r="AU32" s="13"/>
-      <c r="AV32" s="14"/>
+      <c r="AU32" s="13" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV32" s="14" t="inlineStr">
+        <is>
+          <t>深圳市 南山区 广东 518000 CN</t>
+        </is>
+      </c>
       <c r="AW32" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A23BRZJD26C30N</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1CO438NU9H9Y</t>
         </is>
       </c>
       <c r="AX32" s="13"/>
@@ -12511,11 +12545,7 @@
       <c r="AZ32" s="13"/>
       <c r="BA32" s="13"/>
       <c r="BB32" s="13"/>
-      <c r="BC32" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC32" s="13"/>
       <c r="BD32" s="13"/>
       <c r="BE32" s="13"/>
       <c r="BF32" s="13"/>
@@ -12524,25 +12554,49 @@
       <c r="BI32" s="23"/>
       <c r="BJ32" s="23" t="inlineStr">
         <is>
-          <t>2,33 Kilograms</t>
+          <t>1.3 kg</t>
         </is>
       </c>
       <c r="BK32" s="23" t="inlineStr">
         <is>
-          <t>2.33 kg</t>
+          <t>1.30 kg</t>
         </is>
       </c>
       <c r="BL32" s="23" t="inlineStr">
         <is>
-          <t>30L x 24,5l x 23H centimètres</t>
-        </is>
-      </c>
-      <c r="BM32" s="23"/>
-      <c r="BN32" s="23"/>
-      <c r="BO32" s="23"/>
-      <c r="BP32" s="23"/>
-      <c r="BQ32" s="23"/>
-      <c r="BR32" s="13"/>
+          <t>28 x 27 x 11 cm</t>
+        </is>
+      </c>
+      <c r="BM32" s="23" t="inlineStr">
+        <is>
+          <t>28.00 x 27.00 x 11.00 cm</t>
+        </is>
+      </c>
+      <c r="BN32" s="23" t="inlineStr">
+        <is>
+          <t>1.3 kg</t>
+        </is>
+      </c>
+      <c r="BO32" s="23" t="inlineStr">
+        <is>
+          <t>1.30 kg</t>
+        </is>
+      </c>
+      <c r="BP32" s="23" t="inlineStr">
+        <is>
+          <t>28 x 27 x 17 cm</t>
+        </is>
+      </c>
+      <c r="BQ32" s="23" t="inlineStr">
+        <is>
+          <t>28.00 x 27.00 x 17.00 cm</t>
+        </is>
+      </c>
+      <c r="BR32" s="13" t="inlineStr">
+        <is>
+          <t>标准包裹</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="13">
@@ -12551,145 +12605,83 @@
       <c r="B33" s="13"/>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>B0GF7CNTYL</t>
+          <t>B0GGBLWNRZ</t>
         </is>
       </c>
       <c r="D33" s="14"/>
       <c r="E33" s="14"/>
-      <c r="F33" s="14" t="inlineStr">
-        <is>
-          <t>Liwankaqi</t>
-        </is>
-      </c>
+      <c r="F33" s="14"/>
       <c r="G33" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Liwankaqi</t>
+          <t>https://www.amazon.frundefined</t>
         </is>
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>Aspirateur de Matelas UV-C Ultrasonique pour Lit et CanapésAspirateur sans fil pour housses de couette, matelas, canapés en</t>
+          <t>Ubric Aspirateur sans fil anti-acariens, avec filtre HEPA, aspirateur de matelas sans fil pour matelas, canapé, coussin, tapi</t>
         </is>
       </c>
       <c r="I33" s="14"/>
       <c r="J33" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GF7CNTYL?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GGBLWNRZ?psc=1</t>
         </is>
       </c>
       <c r="K33" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71H9bRmoUnL._AC_US600_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/41xNIs1B-1L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L33" s="14" t="inlineStr">
         <is>
-          <t>B0GF7CNTYL</t>
-        </is>
-      </c>
-      <c r="M33" s="14" t="inlineStr">
-        <is>
-          <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Aspirateurs:Aspirateurs pour futons</t>
-        </is>
-      </c>
-      <c r="N33" s="14" t="inlineStr">
-        <is>
-          <t>Voir les 100 premiers en Cuisine et Maison</t>
-        </is>
-      </c>
-      <c r="O33" s="15">
-        <v>1833198</v>
-      </c>
+          <t>B0GGBLWNRZ</t>
+        </is>
+      </c>
+      <c r="M33" s="14"/>
+      <c r="N33" s="14"/>
+      <c r="O33" s="15"/>
       <c r="P33" s="15"/>
-      <c r="Q33" s="16">
-        <v>0</v>
-      </c>
-      <c r="R33" s="17" t="inlineStr">
-        <is>
-          <t>Aspirateurs pour futons</t>
-        </is>
-      </c>
-      <c r="S33" s="18" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
+      <c r="Q33" s="16"/>
+      <c r="R33" s="17"/>
+      <c r="S33" s="18"/>
       <c r="T33" s="15"/>
       <c r="U33" s="16"/>
       <c r="V33" s="15"/>
       <c r="W33" s="15"/>
       <c r="X33" s="15"/>
-      <c r="Y33" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z33" s="20">
-        <v>49.99</v>
-      </c>
+      <c r="Y33" s="19"/>
+      <c r="Z33" s="20"/>
       <c r="AA33"/>
       <c r="AB33"/>
       <c r="AC33" s="2"/>
       <c r="AD33" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE33" s="15"/>
       <c r="AF33" s="21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG33" s="22">
         <v>0</v>
       </c>
-      <c r="AH33" s="20">
-        <v>7.29</v>
-      </c>
+      <c r="AH33" s="20"/>
       <c r="AI33" s="16">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="AJ33"/>
-      <c r="AK33" s="13" t="inlineStr">
-        <is>
-          <t>2026-04-12</t>
-        </is>
-      </c>
-      <c r="AL33" s="19">
-        <v>178</v>
-      </c>
-      <c r="AM33" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
+      <c r="AK33" s="13"/>
+      <c r="AL33" s="19"/>
+      <c r="AM33" s="13"/>
       <c r="AN33" s="13"/>
       <c r="AO33" s="13"/>
       <c r="AP33"/>
       <c r="AQ33" s="19"/>
-      <c r="AR33" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS33" s="14" t="inlineStr">
-        <is>
-          <t>liwantech</t>
-        </is>
-      </c>
-      <c r="AT33" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU33" s="13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV33" s="14" t="inlineStr">
-        <is>
-          <t>深圳市 南山区 广东 518000 CN</t>
-        </is>
-      </c>
-      <c r="AW33" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1CO438NU9H9Y</t>
-        </is>
-      </c>
+      <c r="AR33" s="19"/>
+      <c r="AS33" s="14"/>
+      <c r="AT33" s="13"/>
+      <c r="AU33" s="13"/>
+      <c r="AV33" s="14"/>
+      <c r="AW33" s="13"/>
       <c r="AX33" s="13"/>
       <c r="AY33" s="13"/>
       <c r="AZ33" s="13"/>
@@ -12702,51 +12694,15 @@
       <c r="BG33" s="13"/>
       <c r="BH33" s="14"/>
       <c r="BI33" s="23"/>
-      <c r="BJ33" s="23" t="inlineStr">
-        <is>
-          <t>1.3 kg</t>
-        </is>
-      </c>
-      <c r="BK33" s="23" t="inlineStr">
-        <is>
-          <t>1.30 kg</t>
-        </is>
-      </c>
-      <c r="BL33" s="23" t="inlineStr">
-        <is>
-          <t>28 x 27 x 11 cm</t>
-        </is>
-      </c>
-      <c r="BM33" s="23" t="inlineStr">
-        <is>
-          <t>28.00 x 27.00 x 11.00 cm</t>
-        </is>
-      </c>
-      <c r="BN33" s="23" t="inlineStr">
-        <is>
-          <t>1.3 kg</t>
-        </is>
-      </c>
-      <c r="BO33" s="23" t="inlineStr">
-        <is>
-          <t>1.30 kg</t>
-        </is>
-      </c>
-      <c r="BP33" s="23" t="inlineStr">
-        <is>
-          <t>28 x 27 x 17 cm</t>
-        </is>
-      </c>
-      <c r="BQ33" s="23" t="inlineStr">
-        <is>
-          <t>28.00 x 27.00 x 17.00 cm</t>
-        </is>
-      </c>
-      <c r="BR33" s="13" t="inlineStr">
-        <is>
-          <t>标准包裹</t>
-        </is>
-      </c>
+      <c r="BJ33" s="23"/>
+      <c r="BK33" s="23"/>
+      <c r="BL33" s="23"/>
+      <c r="BM33" s="23"/>
+      <c r="BN33" s="23"/>
+      <c r="BO33" s="23"/>
+      <c r="BP33" s="23"/>
+      <c r="BQ33" s="23"/>
+      <c r="BR33" s="13"/>
     </row>
     <row r="34" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="13">
@@ -12755,7 +12711,7 @@
       <c r="B34" s="13"/>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>B0GGBLWNRZ</t>
+          <t>B0GMPVWCZM</t>
         </is>
       </c>
       <c r="D34" s="14"/>
@@ -12768,23 +12724,23 @@
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>Ubric Aspirateur sans fil anti-acariens, avec filtre HEPA, aspirateur de matelas sans fil pour matelas, canapé, coussin, tapi</t>
+          <t>Elecbee Aspirateur anti-acariens sans fil pour matelas, aspirateur anti-acariens avec lumière UV, indicateur LED, technologie</t>
         </is>
       </c>
       <c r="I34" s="14"/>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GGBLWNRZ?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GMPVWCZM?psc=1</t>
         </is>
       </c>
       <c r="K34" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/41xNIs1B-1L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/81J2yw2XZnL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>B0GGBLWNRZ</t>
+          <t>B0GMPVWCZM</t>
         </is>
       </c>
       <c r="M34" s="14"/>
@@ -12805,11 +12761,11 @@
       <c r="AB34"/>
       <c r="AC34" s="2"/>
       <c r="AD34" s="19">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="AE34" s="15"/>
       <c r="AF34" s="21">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="AG34" s="22">
         <v>0</v>
@@ -12861,104 +12817,212 @@
       <c r="B35" s="13"/>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>B0GMPVWCZM</t>
+          <t>B0GT17NK5X</t>
         </is>
       </c>
       <c r="D35" s="14"/>
       <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
+      <c r="F35" s="14" t="inlineStr">
+        <is>
+          <t>XINYUDAILY</t>
+        </is>
+      </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.frundefined</t>
+          <t>https://www.amazon.fr/XINYUDAILY/b/ref=bl_dp_s_web_85011884031?ie=UTF8&amp;node=85011884031&amp;field-lbr_brands_browse-bin=XINYUDAILY</t>
         </is>
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>Elecbee Aspirateur anti-acariens sans fil pour matelas, aspirateur anti-acariens avec lumière UV, indicateur LED, technologie</t>
+          <t>Aspirateur anti-acariens sans fil pour matelas, avec lumière UV de 253,7 nm, ultrasons et tapotements de rouleau de brosse, a</t>
         </is>
       </c>
       <c r="I35" s="14"/>
       <c r="J35" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GMPVWCZM?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GT17NK5X?psc=1</t>
         </is>
       </c>
       <c r="K35" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/81J2yw2XZnL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71ZkgBFQnaL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L35" s="14" t="inlineStr">
         <is>
-          <t>B0GMPVWCZM</t>
-        </is>
-      </c>
-      <c r="M35" s="14"/>
-      <c r="N35" s="14"/>
-      <c r="O35" s="15"/>
-      <c r="P35" s="15"/>
-      <c r="Q35" s="16"/>
-      <c r="R35" s="17"/>
-      <c r="S35" s="18"/>
+          <t>B0GT17NK5X</t>
+        </is>
+      </c>
+      <c r="M35" s="14" t="inlineStr">
+        <is>
+          <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Aspirateurs:Aspirateurs pour futons</t>
+        </is>
+      </c>
+      <c r="N35" s="14" t="inlineStr">
+        <is>
+          <t>Voir les 100 premiers en Cuisine et Maison</t>
+        </is>
+      </c>
+      <c r="O35" s="15">
+        <v>498895</v>
+      </c>
+      <c r="P35" s="15">
+        <v>719726</v>
+      </c>
+      <c r="Q35" s="16">
+        <v>0.59</v>
+      </c>
+      <c r="R35" s="17" t="inlineStr">
+        <is>
+          <t>Aspirateurs pour futons</t>
+        </is>
+      </c>
+      <c r="S35" s="18" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="T35" s="15"/>
       <c r="U35" s="16"/>
       <c r="V35" s="15"/>
       <c r="W35" s="15"/>
       <c r="X35" s="15"/>
-      <c r="Y35" s="19"/>
-      <c r="Z35" s="20"/>
+      <c r="Y35" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z35" s="20">
+        <v>69.99</v>
+      </c>
       <c r="AA35"/>
       <c r="AB35"/>
       <c r="AC35" s="2"/>
       <c r="AD35" s="19">
-        <v>24</v>
-      </c>
-      <c r="AE35" s="15"/>
+        <v>3</v>
+      </c>
+      <c r="AE35" s="15">
+        <v>0</v>
+      </c>
       <c r="AF35" s="21">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AG35" s="22">
         <v>0</v>
       </c>
-      <c r="AH35" s="20"/>
+      <c r="AH35" s="20">
+        <v>8.03</v>
+      </c>
       <c r="AI35" s="16">
-        <v>0</v>
+        <v>0.74</v>
       </c>
       <c r="AJ35"/>
-      <c r="AK35" s="13"/>
-      <c r="AL35" s="19"/>
-      <c r="AM35" s="13"/>
+      <c r="AK35" s="13" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AL35" s="19">
+        <v>170</v>
+      </c>
+      <c r="AM35" s="13" t="inlineStr">
+        <is>
+          <t>FBA</t>
+        </is>
+      </c>
       <c r="AN35" s="13"/>
       <c r="AO35" s="13"/>
       <c r="AP35"/>
-      <c r="AQ35" s="19"/>
-      <c r="AR35" s="19"/>
-      <c r="AS35" s="14"/>
-      <c r="AT35" s="13"/>
-      <c r="AU35" s="13"/>
-      <c r="AV35" s="14"/>
-      <c r="AW35" s="13"/>
+      <c r="AQ35" s="19">
+        <v>8</v>
+      </c>
+      <c r="AR35" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS35" s="14" t="inlineStr">
+        <is>
+          <t>XINYU-EU</t>
+        </is>
+      </c>
+      <c r="AT35" s="13" t="inlineStr">
+        <is>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="AU35" s="13" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV35" s="14" t="inlineStr">
+        <is>
+          <t>营口市 鲅鱼圈区 辽宁省 115007 CN</t>
+        </is>
+      </c>
+      <c r="AW35" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AD38JSQ91A5LY</t>
+        </is>
+      </c>
       <c r="AX35" s="13"/>
       <c r="AY35" s="13"/>
       <c r="AZ35" s="13"/>
       <c r="BA35" s="13"/>
       <c r="BB35" s="13"/>
       <c r="BC35" s="13"/>
-      <c r="BD35" s="13"/>
+      <c r="BD35" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE35" s="13"/>
       <c r="BF35" s="13"/>
       <c r="BG35" s="13"/>
       <c r="BH35" s="14"/>
       <c r="BI35" s="23"/>
-      <c r="BJ35" s="23"/>
-      <c r="BK35" s="23"/>
-      <c r="BL35" s="23"/>
-      <c r="BM35" s="23"/>
-      <c r="BN35" s="23"/>
-      <c r="BO35" s="23"/>
-      <c r="BP35" s="23"/>
-      <c r="BQ35" s="23"/>
-      <c r="BR35" s="13"/>
+      <c r="BJ35" s="23" t="inlineStr">
+        <is>
+          <t>2,2 Kilograms</t>
+        </is>
+      </c>
+      <c r="BK35" s="23" t="inlineStr">
+        <is>
+          <t>2.20 kg</t>
+        </is>
+      </c>
+      <c r="BL35" s="23" t="inlineStr">
+        <is>
+          <t>32 x 29 x 21 cm</t>
+        </is>
+      </c>
+      <c r="BM35" s="23" t="inlineStr">
+        <is>
+          <t>32.00 x 29.00 x 21.00 cm</t>
+        </is>
+      </c>
+      <c r="BN35" s="23" t="inlineStr">
+        <is>
+          <t>2.2 kg</t>
+        </is>
+      </c>
+      <c r="BO35" s="23" t="inlineStr">
+        <is>
+          <t>2.20 kg</t>
+        </is>
+      </c>
+      <c r="BP35" s="23" t="inlineStr">
+        <is>
+          <t>32 x 29 x 21 cm</t>
+        </is>
+      </c>
+      <c r="BQ35" s="23" t="inlineStr">
+        <is>
+          <t>32.00 x 29.00 x 21.00 cm</t>
+        </is>
+      </c>
+      <c r="BR35" s="13" t="inlineStr">
+        <is>
+          <t>标准包裹</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="13">
@@ -12967,40 +13031,40 @@
       <c r="B36" s="13"/>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>B0GT17NK5X</t>
+          <t>B0GWH1FGJB</t>
         </is>
       </c>
       <c r="D36" s="14"/>
       <c r="E36" s="14"/>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>XINYUDAILY</t>
+          <t>Timisea</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/XINYUDAILY/b/ref=bl_dp_s_web_85011884031?ie=UTF8&amp;node=85011884031&amp;field-lbr_brands_browse-bin=XINYUDAILY</t>
+          <t>https://www.amazon.fr/Timisea/b/ref=bl_dp_s_web_93230377031?ie=UTF8&amp;node=93230377031&amp;field-lbr_brands_browse-bin=Timisea</t>
         </is>
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>Aspirateur anti-acariens sans fil pour matelas, avec lumière UV de 253,7 nm, ultrasons et tapotements de rouleau de brosse, a</t>
+          <t>Aspirateur anti-acariens 2 en 1 pour matelas, stérilisation à lumière bleue et haute fréquence, puissant nettoyeur de matelas</t>
         </is>
       </c>
       <c r="I36" s="14"/>
       <c r="J36" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GT17NK5X?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GWH1FGJB?psc=1</t>
         </is>
       </c>
       <c r="K36" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71ZkgBFQnaL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/31txErJ7TmL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>B0GT17NK5X</t>
+          <t>B0GWH1FGJB</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
@@ -13014,13 +13078,11 @@
         </is>
       </c>
       <c r="O36" s="15">
-        <v>498895</v>
-      </c>
-      <c r="P36" s="15">
-        <v>719726</v>
-      </c>
+        <v>398530</v>
+      </c>
+      <c r="P36" s="15"/>
       <c r="Q36" s="16">
-        <v>0.59</v>
+        <v>0</v>
       </c>
       <c r="R36" s="17" t="inlineStr">
         <is>
@@ -13029,7 +13091,7 @@
       </c>
       <c r="S36" s="18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="T36" s="15"/>
@@ -13041,75 +13103,59 @@
         <v>1</v>
       </c>
       <c r="Z36" s="20">
-        <v>69.99</v>
+        <v>35.99</v>
       </c>
       <c r="AA36"/>
       <c r="AB36"/>
       <c r="AC36" s="2"/>
-      <c r="AD36" s="19">
-        <v>3</v>
-      </c>
+      <c r="AD36" s="19"/>
       <c r="AE36" s="15">
         <v>0</v>
       </c>
-      <c r="AF36" s="21">
-        <v>4.2</v>
-      </c>
+      <c r="AF36" s="21"/>
       <c r="AG36" s="22">
         <v>0</v>
       </c>
-      <c r="AH36" s="20">
-        <v>8.03</v>
-      </c>
+      <c r="AH36" s="20"/>
       <c r="AI36" s="16">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="AJ36"/>
       <c r="AK36" s="13" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AL36" s="19">
-        <v>170</v>
+        <v>63</v>
       </c>
       <c r="AM36" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN36" s="13"/>
       <c r="AO36" s="13"/>
       <c r="AP36"/>
-      <c r="AQ36" s="19">
-        <v>8</v>
-      </c>
+      <c r="AQ36" s="19"/>
       <c r="AR36" s="19">
         <v>1</v>
       </c>
       <c r="AS36" s="14" t="inlineStr">
         <is>
-          <t>XINYU-EU</t>
+          <t>Alloplectus</t>
         </is>
       </c>
       <c r="AT36" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU36" s="13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV36" s="14" t="inlineStr">
-        <is>
-          <t>营口市 鲅鱼圈区 辽宁省 115007 CN</t>
-        </is>
-      </c>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU36" s="13"/>
+      <c r="AV36" s="14"/>
       <c r="AW36" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AD38JSQ91A5LY</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3SPQY2QF85KOQ</t>
         </is>
       </c>
       <c r="AX36" s="13"/>
@@ -13118,11 +13164,7 @@
       <c r="BA36" s="13"/>
       <c r="BB36" s="13"/>
       <c r="BC36" s="13"/>
-      <c r="BD36" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD36" s="13"/>
       <c r="BE36" s="13"/>
       <c r="BF36" s="13"/>
       <c r="BG36" s="13"/>
@@ -13130,49 +13172,25 @@
       <c r="BI36" s="23"/>
       <c r="BJ36" s="23" t="inlineStr">
         <is>
-          <t>2,2 Kilograms</t>
+          <t>855 g</t>
         </is>
       </c>
       <c r="BK36" s="23" t="inlineStr">
         <is>
-          <t>2.20 kg</t>
+          <t>855.00 g</t>
         </is>
       </c>
       <c r="BL36" s="23" t="inlineStr">
         <is>
-          <t>32 x 29 x 21 cm</t>
-        </is>
-      </c>
-      <c r="BM36" s="23" t="inlineStr">
-        <is>
-          <t>32.00 x 29.00 x 21.00 cm</t>
-        </is>
-      </c>
-      <c r="BN36" s="23" t="inlineStr">
-        <is>
-          <t>2.2 kg</t>
-        </is>
-      </c>
-      <c r="BO36" s="23" t="inlineStr">
-        <is>
-          <t>2.20 kg</t>
-        </is>
-      </c>
-      <c r="BP36" s="23" t="inlineStr">
-        <is>
-          <t>32 x 29 x 21 cm</t>
-        </is>
-      </c>
-      <c r="BQ36" s="23" t="inlineStr">
-        <is>
-          <t>32.00 x 29.00 x 21.00 cm</t>
-        </is>
-      </c>
-      <c r="BR36" s="13" t="inlineStr">
-        <is>
-          <t>标准包裹</t>
-        </is>
-      </c>
+          <t>21L x 8l x 37H centimètres</t>
+        </is>
+      </c>
+      <c r="BM36" s="23"/>
+      <c r="BN36" s="23"/>
+      <c r="BO36" s="23"/>
+      <c r="BP36" s="23"/>
+      <c r="BQ36" s="23"/>
+      <c r="BR36" s="13"/>
     </row>
     <row r="37" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="13">
@@ -13181,40 +13199,40 @@
       <c r="B37" s="13"/>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>B0GWH1FGJB</t>
+          <t>B0GYS43G8G</t>
         </is>
       </c>
       <c r="D37" s="14"/>
       <c r="E37" s="14"/>
       <c r="F37" s="14" t="inlineStr">
         <is>
-          <t>Timisea</t>
+          <t>ALLILUYAA</t>
         </is>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/Timisea/b/ref=bl_dp_s_web_93230377031?ie=UTF8&amp;node=93230377031&amp;field-lbr_brands_browse-bin=Timisea</t>
+          <t>https://www.amazon.fr/stores/ALLILUYAA/page/B6AAB331-17D2-444A-B3E5-494EC94DE846?lp_asin=B0GYS43G8G&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
-          <t>Aspirateur anti-acariens 2 en 1 pour matelas, stérilisation à lumière bleue et haute fréquence, puissant nettoyeur de matelas</t>
+          <t>Aspirateur Matelas, Aspirateur Anti-Acariens, Vibration Haute Fréquence, Filtrage Trois Niveaux, Filtre Lavable, pour Canapés</t>
         </is>
       </c>
       <c r="I37" s="14"/>
       <c r="J37" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GWH1FGJB?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GYS43G8G?psc=1</t>
         </is>
       </c>
       <c r="K37" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31txErJ7TmL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/51JXrvAAoZL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L37" s="14" t="inlineStr">
         <is>
-          <t>B0GWH1FGJB</t>
+          <t>B0GYS43G8G</t>
         </is>
       </c>
       <c r="M37" s="14" t="inlineStr">
@@ -13228,11 +13246,13 @@
         </is>
       </c>
       <c r="O37" s="15">
-        <v>398530</v>
-      </c>
-      <c r="P37" s="15"/>
+        <v>1102206</v>
+      </c>
+      <c r="P37" s="15">
+        <v>-21169</v>
+      </c>
       <c r="Q37" s="16">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="R37" s="17" t="inlineStr">
         <is>
@@ -13241,7 +13261,7 @@
       </c>
       <c r="S37" s="18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>29</t>
         </is>
       </c>
       <c r="T37" s="15"/>
@@ -13253,31 +13273,37 @@
         <v>1</v>
       </c>
       <c r="Z37" s="20">
-        <v>35.99</v>
+        <v>25.99</v>
       </c>
       <c r="AA37"/>
       <c r="AB37"/>
       <c r="AC37" s="2"/>
-      <c r="AD37" s="19"/>
+      <c r="AD37" s="19">
+        <v>2</v>
+      </c>
       <c r="AE37" s="15">
         <v>0</v>
       </c>
-      <c r="AF37" s="21"/>
+      <c r="AF37" s="21">
+        <v>1</v>
+      </c>
       <c r="AG37" s="22">
         <v>0</v>
       </c>
-      <c r="AH37" s="20"/>
+      <c r="AH37" s="20">
+        <v>6.06</v>
+      </c>
       <c r="AI37" s="16">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="AJ37"/>
       <c r="AK37" s="13" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="AL37" s="19">
-        <v>63</v>
+        <v>130</v>
       </c>
       <c r="AM37" s="13" t="inlineStr">
         <is>
@@ -13287,13 +13313,15 @@
       <c r="AN37" s="13"/>
       <c r="AO37" s="13"/>
       <c r="AP37"/>
-      <c r="AQ37" s="19"/>
+      <c r="AQ37" s="19">
+        <v>7</v>
+      </c>
       <c r="AR37" s="19">
         <v>1</v>
       </c>
       <c r="AS37" s="14" t="inlineStr">
         <is>
-          <t>Alloplectus</t>
+          <t>ALLILUYAA</t>
         </is>
       </c>
       <c r="AT37" s="13" t="inlineStr">
@@ -13301,11 +13329,19 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="AU37" s="13"/>
-      <c r="AV37" s="14"/>
+      <c r="AU37" s="13" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV37" s="14" t="inlineStr">
+        <is>
+          <t>bayuquan LiaoNing 115007 CN</t>
+        </is>
+      </c>
       <c r="AW37" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3SPQY2QF85KOQ</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A238ODZG8O3E58</t>
         </is>
       </c>
       <c r="AX37" s="13"/>
@@ -13322,25 +13358,49 @@
       <c r="BI37" s="23"/>
       <c r="BJ37" s="23" t="inlineStr">
         <is>
-          <t>855 g</t>
+          <t>430 g</t>
         </is>
       </c>
       <c r="BK37" s="23" t="inlineStr">
         <is>
-          <t>855.00 g</t>
+          <t>430.00 g</t>
         </is>
       </c>
       <c r="BL37" s="23" t="inlineStr">
         <is>
-          <t>21L x 8l x 37H centimètres</t>
-        </is>
-      </c>
-      <c r="BM37" s="23"/>
-      <c r="BN37" s="23"/>
-      <c r="BO37" s="23"/>
-      <c r="BP37" s="23"/>
-      <c r="BQ37" s="23"/>
-      <c r="BR37" s="13"/>
+          <t>1 x 1 x 1 cm</t>
+        </is>
+      </c>
+      <c r="BM37" s="23" t="inlineStr">
+        <is>
+          <t>1.00 x 1.00 x 1.00 cm</t>
+        </is>
+      </c>
+      <c r="BN37" s="23" t="inlineStr">
+        <is>
+          <t>430 g</t>
+        </is>
+      </c>
+      <c r="BO37" s="23" t="inlineStr">
+        <is>
+          <t>430.00 g</t>
+        </is>
+      </c>
+      <c r="BP37" s="23" t="inlineStr">
+        <is>
+          <t>25.1 x 20.5 x 11.2 cm</t>
+        </is>
+      </c>
+      <c r="BQ37" s="23" t="inlineStr">
+        <is>
+          <t>25.10 x 20.50 x 11.20 cm</t>
+        </is>
+      </c>
+      <c r="BR37" s="13" t="inlineStr">
+        <is>
+          <t>小包裹</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="13">
@@ -13349,151 +13409,83 @@
       <c r="B38" s="13"/>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>B0GYS43G8G</t>
+          <t>B0H6F2NPXK</t>
         </is>
       </c>
       <c r="D38" s="14"/>
       <c r="E38" s="14"/>
-      <c r="F38" s="14" t="inlineStr">
-        <is>
-          <t>ALLILUYAA</t>
-        </is>
-      </c>
+      <c r="F38" s="14"/>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/stores/ALLILUYAA/page/B6AAB331-17D2-444A-B3E5-494EC94DE846?lp_asin=B0GYS43G8G&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.frundefined</t>
         </is>
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>Aspirateur Matelas, Aspirateur Anti-Acariens, Vibration Haute Fréquence, Filtrage Trois Niveaux, Filtre Lavable, pour Canapés</t>
+          <t>Lubluelu Nettoyeur de matelas 3 en 1 20 kPa, aspirateur anti-acariens avec fonction de frappe et fonction chauffante, aspirat</t>
         </is>
       </c>
       <c r="I38" s="14"/>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GYS43G8G?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0H6F2NPXK?psc=1</t>
         </is>
       </c>
       <c r="K38" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51JXrvAAoZL._AC_US600_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61InrYvl2-L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>B0GYS43G8G</t>
-        </is>
-      </c>
-      <c r="M38" s="14" t="inlineStr">
-        <is>
-          <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Aspirateurs:Aspirateurs pour futons</t>
-        </is>
-      </c>
-      <c r="N38" s="14" t="inlineStr">
-        <is>
-          <t>Voir les 100 premiers en Cuisine et Maison</t>
-        </is>
-      </c>
-      <c r="O38" s="15">
-        <v>1102206</v>
-      </c>
-      <c r="P38" s="15">
-        <v>-21169</v>
-      </c>
-      <c r="Q38" s="16">
-        <v>-0.02</v>
-      </c>
-      <c r="R38" s="17" t="inlineStr">
-        <is>
-          <t>Aspirateurs pour futons</t>
-        </is>
-      </c>
-      <c r="S38" s="18" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+          <t>B0H6F2NPXK</t>
+        </is>
+      </c>
+      <c r="M38" s="14"/>
+      <c r="N38" s="14"/>
+      <c r="O38" s="15"/>
+      <c r="P38" s="15"/>
+      <c r="Q38" s="16"/>
+      <c r="R38" s="17"/>
+      <c r="S38" s="18"/>
       <c r="T38" s="15"/>
       <c r="U38" s="16"/>
       <c r="V38" s="15"/>
       <c r="W38" s="15"/>
       <c r="X38" s="15"/>
-      <c r="Y38" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z38" s="20">
-        <v>25.99</v>
-      </c>
+      <c r="Y38" s="19"/>
+      <c r="Z38" s="20"/>
       <c r="AA38"/>
       <c r="AB38"/>
       <c r="AC38" s="2"/>
       <c r="AD38" s="19">
-        <v>2</v>
-      </c>
-      <c r="AE38" s="15">
-        <v>0</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="AE38" s="15"/>
       <c r="AF38" s="21">
-        <v>1</v>
+        <v>4.6</v>
       </c>
       <c r="AG38" s="22">
         <v>0</v>
       </c>
-      <c r="AH38" s="20">
-        <v>6.06</v>
-      </c>
+      <c r="AH38" s="20"/>
       <c r="AI38" s="16">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="AJ38"/>
-      <c r="AK38" s="13" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="AL38" s="19">
-        <v>130</v>
-      </c>
-      <c r="AM38" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="AK38" s="13"/>
+      <c r="AL38" s="19"/>
+      <c r="AM38" s="13"/>
       <c r="AN38" s="13"/>
       <c r="AO38" s="13"/>
       <c r="AP38"/>
-      <c r="AQ38" s="19">
-        <v>7</v>
-      </c>
-      <c r="AR38" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS38" s="14" t="inlineStr">
-        <is>
-          <t>ALLILUYAA</t>
-        </is>
-      </c>
-      <c r="AT38" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU38" s="13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV38" s="14" t="inlineStr">
-        <is>
-          <t>bayuquan LiaoNing 115007 CN</t>
-        </is>
-      </c>
-      <c r="AW38" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A238ODZG8O3E58</t>
-        </is>
-      </c>
+      <c r="AQ38" s="19"/>
+      <c r="AR38" s="19"/>
+      <c r="AS38" s="14"/>
+      <c r="AT38" s="13"/>
+      <c r="AU38" s="13"/>
+      <c r="AV38" s="14"/>
+      <c r="AW38" s="13"/>
       <c r="AX38" s="13"/>
       <c r="AY38" s="13"/>
       <c r="AZ38" s="13"/>
@@ -13506,51 +13498,15 @@
       <c r="BG38" s="13"/>
       <c r="BH38" s="14"/>
       <c r="BI38" s="23"/>
-      <c r="BJ38" s="23" t="inlineStr">
-        <is>
-          <t>430 g</t>
-        </is>
-      </c>
-      <c r="BK38" s="23" t="inlineStr">
-        <is>
-          <t>430.00 g</t>
-        </is>
-      </c>
-      <c r="BL38" s="23" t="inlineStr">
-        <is>
-          <t>1 x 1 x 1 cm</t>
-        </is>
-      </c>
-      <c r="BM38" s="23" t="inlineStr">
-        <is>
-          <t>1.00 x 1.00 x 1.00 cm</t>
-        </is>
-      </c>
-      <c r="BN38" s="23" t="inlineStr">
-        <is>
-          <t>430 g</t>
-        </is>
-      </c>
-      <c r="BO38" s="23" t="inlineStr">
-        <is>
-          <t>430.00 g</t>
-        </is>
-      </c>
-      <c r="BP38" s="23" t="inlineStr">
-        <is>
-          <t>25.1 x 20.5 x 11.2 cm</t>
-        </is>
-      </c>
-      <c r="BQ38" s="23" t="inlineStr">
-        <is>
-          <t>25.10 x 20.50 x 11.20 cm</t>
-        </is>
-      </c>
-      <c r="BR38" s="13" t="inlineStr">
-        <is>
-          <t>小包裹</t>
-        </is>
-      </c>
+      <c r="BJ38" s="23"/>
+      <c r="BK38" s="23"/>
+      <c r="BL38" s="23"/>
+      <c r="BM38" s="23"/>
+      <c r="BN38" s="23"/>
+      <c r="BO38" s="23"/>
+      <c r="BP38" s="23"/>
+      <c r="BQ38" s="23"/>
+      <c r="BR38" s="13"/>
     </row>
     <row r="39" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="13">
@@ -13559,39 +13515,47 @@
       <c r="B39" s="13"/>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>B0H6F2NPXK</t>
+          <t>B0H712ZM35</t>
         </is>
       </c>
       <c r="D39" s="14"/>
       <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
+      <c r="F39" s="14" t="inlineStr">
+        <is>
+          <t>Resmafn</t>
+        </is>
+      </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.frundefined</t>
+          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Resmafn</t>
         </is>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>Lubluelu Nettoyeur de matelas 3 en 1 20 kPa, aspirateur anti-acariens avec fonction de frappe et fonction chauffante, aspirat</t>
+          <t>Resmafn Aspirateur Anti Acariens avec UV C, 15KPa Puissance Aspirateur Lit avec 5M Fil, 60°C Chaleur, Réservoir Amovible 1L a</t>
         </is>
       </c>
       <c r="I39" s="14"/>
       <c r="J39" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0H6F2NPXK?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0H712ZM35?psc=1</t>
         </is>
       </c>
       <c r="K39" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61InrYvl2-L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41lzTiHI9yL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L39" s="14" t="inlineStr">
         <is>
-          <t>B0H6F2NPXK</t>
-        </is>
-      </c>
-      <c r="M39" s="14"/>
+          <t>B0H712ZM35</t>
+        </is>
+      </c>
+      <c r="M39" s="14" t="inlineStr">
+        <is>
+          <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Aspirateurs:Aspirateurs pour futons</t>
+        </is>
+      </c>
       <c r="N39" s="14"/>
       <c r="O39" s="15"/>
       <c r="P39" s="15"/>
@@ -13603,17 +13567,23 @@
       <c r="V39" s="15"/>
       <c r="W39" s="15"/>
       <c r="X39" s="15"/>
-      <c r="Y39" s="19"/>
-      <c r="Z39" s="20"/>
+      <c r="Y39" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z39" s="20">
+        <v>49.99</v>
+      </c>
       <c r="AA39"/>
       <c r="AB39"/>
       <c r="AC39" s="2"/>
       <c r="AD39" s="19">
-        <v>25</v>
-      </c>
-      <c r="AE39" s="15"/>
+        <v>18</v>
+      </c>
+      <c r="AE39" s="15">
+        <v>0</v>
+      </c>
       <c r="AF39" s="21">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AG39" s="22">
         <v>0</v>
@@ -13623,33 +13593,69 @@
         <v>0</v>
       </c>
       <c r="AJ39"/>
-      <c r="AK39" s="13"/>
-      <c r="AL39" s="19"/>
-      <c r="AM39" s="13"/>
+      <c r="AK39" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AL39" s="19">
+        <v>20</v>
+      </c>
+      <c r="AM39" s="13" t="inlineStr">
+        <is>
+          <t>FBA</t>
+        </is>
+      </c>
       <c r="AN39" s="13"/>
       <c r="AO39" s="13"/>
       <c r="AP39"/>
       <c r="AQ39" s="19"/>
-      <c r="AR39" s="19"/>
-      <c r="AS39" s="14"/>
-      <c r="AT39" s="13"/>
+      <c r="AR39" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS39" s="14" t="inlineStr">
+        <is>
+          <t>STAIK</t>
+        </is>
+      </c>
+      <c r="AT39" s="13" t="inlineStr">
+        <is>
+          <t>FBA</t>
+        </is>
+      </c>
       <c r="AU39" s="13"/>
       <c r="AV39" s="14"/>
-      <c r="AW39" s="13"/>
+      <c r="AW39" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3SB2QKWYM7MS5</t>
+        </is>
+      </c>
       <c r="AX39" s="13"/>
       <c r="AY39" s="13"/>
       <c r="AZ39" s="13"/>
       <c r="BA39" s="13"/>
       <c r="BB39" s="13"/>
-      <c r="BC39" s="13"/>
+      <c r="BC39" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD39" s="13"/>
       <c r="BE39" s="13"/>
       <c r="BF39" s="13"/>
       <c r="BG39" s="13"/>
       <c r="BH39" s="14"/>
       <c r="BI39" s="23"/>
-      <c r="BJ39" s="23"/>
-      <c r="BK39" s="23"/>
+      <c r="BJ39" s="23" t="inlineStr">
+        <is>
+          <t>3,18 Kilograms</t>
+        </is>
+      </c>
+      <c r="BK39" s="23" t="inlineStr">
+        <is>
+          <t>3.18 kg</t>
+        </is>
+      </c>
       <c r="BL39" s="23"/>
       <c r="BM39" s="23"/>
       <c r="BN39" s="23"/>
@@ -13665,40 +13671,40 @@
       <c r="B40" s="13"/>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>B0H712ZM35</t>
+          <t>B0H8XNCYS3</t>
         </is>
       </c>
       <c r="D40" s="14"/>
       <c r="E40" s="14"/>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>Resmafn</t>
+          <t>Umllpet</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Resmafn</t>
+          <t>https://www.amazon.fr/Umllpet/b/ref=bl_dp_s_web_66106680031?ie=UTF8&amp;node=66106680031&amp;field-lbr_brands_browse-bin=Umllpet</t>
         </is>
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>Resmafn Aspirateur Anti Acariens avec UV C, 15KPa Puissance Aspirateur Lit avec 5M Fil, 60°C Chaleur, Réservoir Amovible 1L a</t>
+          <t>Aspirateur anti-acariens pour matelas, lumière UV-C, 20 kPa, aspirateur àsStérilisation UV 253,7 nm, forte puissance d'aspi</t>
         </is>
       </c>
       <c r="I40" s="14"/>
       <c r="J40" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0H712ZM35?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0H8XNCYS3?psc=1</t>
         </is>
       </c>
       <c r="K40" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41lzTiHI9yL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/412ayO2+-bL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>B0H712ZM35</t>
+          <t>B0H8XNCYS3</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
@@ -13721,20 +13727,16 @@
         <v>1</v>
       </c>
       <c r="Z40" s="20">
-        <v>49.99</v>
+        <v>30.53</v>
       </c>
       <c r="AA40"/>
       <c r="AB40"/>
       <c r="AC40" s="2"/>
-      <c r="AD40" s="19">
-        <v>18</v>
-      </c>
+      <c r="AD40" s="19"/>
       <c r="AE40" s="15">
         <v>0</v>
       </c>
-      <c r="AF40" s="21">
-        <v>4.9</v>
-      </c>
+      <c r="AF40" s="21"/>
       <c r="AG40" s="22">
         <v>0</v>
       </c>
@@ -13745,11 +13747,11 @@
       <c r="AJ40"/>
       <c r="AK40" s="13" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AL40" s="19">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AM40" s="13" t="inlineStr">
         <is>
@@ -13765,7 +13767,7 @@
       </c>
       <c r="AS40" s="14" t="inlineStr">
         <is>
-          <t>STAIK</t>
+          <t>Umllpet</t>
         </is>
       </c>
       <c r="AT40" s="13" t="inlineStr">
@@ -13777,7 +13779,7 @@
       <c r="AV40" s="14"/>
       <c r="AW40" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3SB2QKWYM7MS5</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A5NA8IRE5E804</t>
         </is>
       </c>
       <c r="AX40" s="13"/>
@@ -13785,11 +13787,7 @@
       <c r="AZ40" s="13"/>
       <c r="BA40" s="13"/>
       <c r="BB40" s="13"/>
-      <c r="BC40" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC40" s="13"/>
       <c r="BD40" s="13"/>
       <c r="BE40" s="13"/>
       <c r="BF40" s="13"/>
@@ -13798,15 +13796,19 @@
       <c r="BI40" s="23"/>
       <c r="BJ40" s="23" t="inlineStr">
         <is>
-          <t>3,18 Kilograms</t>
+          <t>650 g</t>
         </is>
       </c>
       <c r="BK40" s="23" t="inlineStr">
         <is>
-          <t>3.18 kg</t>
-        </is>
-      </c>
-      <c r="BL40" s="23"/>
+          <t>650.00 g</t>
+        </is>
+      </c>
+      <c r="BL40" s="23" t="inlineStr">
+        <is>
+          <t>25L x 20,4l x 11H centimètres</t>
+        </is>
+      </c>
       <c r="BM40" s="23"/>
       <c r="BN40" s="23"/>
       <c r="BO40" s="23"/>
@@ -13821,40 +13823,40 @@
       <c r="B41" s="13"/>
       <c r="C41" s="14" t="inlineStr">
         <is>
-          <t>B0H8XNCYS3</t>
+          <t>B0H984GBDC</t>
         </is>
       </c>
       <c r="D41" s="14"/>
       <c r="E41" s="14"/>
       <c r="F41" s="14" t="inlineStr">
         <is>
-          <t>Umllpet</t>
+          <t>Xlife</t>
         </is>
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/Umllpet/b/ref=bl_dp_s_web_66106680031?ie=UTF8&amp;node=66106680031&amp;field-lbr_brands_browse-bin=Umllpet</t>
+          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Xlife</t>
         </is>
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
-          <t>Aspirateur anti-acariens pour matelas, lumière UV-C, 20 kPa, aspirateur àsStérilisation UV 253,7 nm, forte puissance d'aspi</t>
+          <t>Xlife Aspirateur anti-acariens pour matelass18 pa, lumière UV-C, air chaud de 63 °C et 2 brosses</t>
         </is>
       </c>
       <c r="I41" s="14"/>
       <c r="J41" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0H8XNCYS3?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0H984GBDC?psc=1</t>
         </is>
       </c>
       <c r="K41" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/412ayO2+-bL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/515qVEbm90L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L41" s="14" t="inlineStr">
         <is>
-          <t>B0H8XNCYS3</t>
+          <t>B0H984GBDC</t>
         </is>
       </c>
       <c r="M41" s="14" t="inlineStr">
@@ -13877,7 +13879,7 @@
         <v>1</v>
       </c>
       <c r="Z41" s="20">
-        <v>30.53</v>
+        <v>102.66</v>
       </c>
       <c r="AA41"/>
       <c r="AB41"/>
@@ -13895,17 +13897,11 @@
         <v>0</v>
       </c>
       <c r="AJ41"/>
-      <c r="AK41" s="13" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AL41" s="19">
-        <v>40</v>
-      </c>
+      <c r="AK41" s="13"/>
+      <c r="AL41" s="19"/>
       <c r="AM41" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN41" s="13"/>
@@ -13917,21 +13913,17 @@
       </c>
       <c r="AS41" s="14" t="inlineStr">
         <is>
-          <t>Umllpet</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT41" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AU41" s="13"/>
       <c r="AV41" s="14"/>
-      <c r="AW41" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A5NA8IRE5E804</t>
-        </is>
-      </c>
+      <c r="AW41" s="13"/>
       <c r="AX41" s="13"/>
       <c r="AY41" s="13"/>
       <c r="AZ41" s="13"/>
@@ -13946,17 +13938,17 @@
       <c r="BI41" s="23"/>
       <c r="BJ41" s="23" t="inlineStr">
         <is>
-          <t>650 g</t>
+          <t>2,69 Kilograms</t>
         </is>
       </c>
       <c r="BK41" s="23" t="inlineStr">
         <is>
-          <t>650.00 g</t>
+          <t>2.69 kg</t>
         </is>
       </c>
       <c r="BL41" s="23" t="inlineStr">
         <is>
-          <t>25L x 20,4l x 11H centimètres</t>
+          <t>29,5L x 22l x 18,2H centimètres</t>
         </is>
       </c>
       <c r="BM41" s="23"/>
@@ -13973,53 +13965,69 @@
       <c r="B42" s="13"/>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>B0H984GBDC</t>
+          <t>B0HFSKFZVX</t>
         </is>
       </c>
       <c r="D42" s="14"/>
       <c r="E42" s="14"/>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>Xlife</t>
+          <t>IERAKOR</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Xlife</t>
+          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=IERAKOR</t>
         </is>
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>Xlife Aspirateur anti-acariens pour matelass18 pa, lumière UV-C, air chaud de 63 °C et 2 brosses</t>
+          <t>IERAKOR Aspirateur Matelas Anti Acariens avec Lumière UV, 16kPa Aspirations600W Aspirateur à Main, Air Chaud 140°F, ultraso</t>
         </is>
       </c>
       <c r="I42" s="14"/>
       <c r="J42" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0H984GBDC?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0HFSKFZVX?psc=1</t>
         </is>
       </c>
       <c r="K42" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/515qVEbm90L._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71XDAjt0gLL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>B0H984GBDC</t>
+          <t>B0HFSKFZVX</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
         <is>
-          <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Aspirateurs:Aspirateurs pour futons</t>
-        </is>
-      </c>
-      <c r="N42" s="14"/>
-      <c r="O42" s="15"/>
+          <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Aspirateurs:Aspirateurs à main</t>
+        </is>
+      </c>
+      <c r="N42" s="14" t="inlineStr">
+        <is>
+          <t>Voir les 100 premiers en Cuisine et Maison</t>
+        </is>
+      </c>
+      <c r="O42" s="15">
+        <v>371717</v>
+      </c>
       <c r="P42" s="15"/>
-      <c r="Q42" s="16"/>
-      <c r="R42" s="17"/>
-      <c r="S42" s="18"/>
+      <c r="Q42" s="16">
+        <v>0</v>
+      </c>
+      <c r="R42" s="17" t="inlineStr">
+        <is>
+          <t>Aspirateurs à main</t>
+        </is>
+      </c>
+      <c r="S42" s="18" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
       <c r="T42" s="15"/>
       <c r="U42" s="16"/>
       <c r="V42" s="15"/>
@@ -14029,76 +14037,100 @@
         <v>1</v>
       </c>
       <c r="Z42" s="20">
-        <v>102.66</v>
+        <v>89.99</v>
       </c>
       <c r="AA42"/>
       <c r="AB42"/>
       <c r="AC42" s="2"/>
-      <c r="AD42" s="19"/>
+      <c r="AD42" s="19">
+        <v>8</v>
+      </c>
       <c r="AE42" s="15">
-        <v>0</v>
-      </c>
-      <c r="AF42" s="21"/>
+        <v>2</v>
+      </c>
+      <c r="AF42" s="21">
+        <v>5</v>
+      </c>
       <c r="AG42" s="22">
         <v>0</v>
       </c>
       <c r="AH42" s="20"/>
       <c r="AI42" s="16">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="AJ42"/>
-      <c r="AK42" s="13"/>
-      <c r="AL42" s="19"/>
+      <c r="AK42" s="13" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AL42" s="19">
+        <v>42</v>
+      </c>
       <c r="AM42" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AN42" s="13"/>
       <c r="AO42" s="13"/>
       <c r="AP42"/>
-      <c r="AQ42" s="19"/>
+      <c r="AQ42" s="19">
+        <v>9</v>
+      </c>
       <c r="AR42" s="19">
         <v>1</v>
       </c>
       <c r="AS42" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>aijuzhang_01</t>
         </is>
       </c>
       <c r="AT42" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU42" s="13"/>
-      <c r="AV42" s="14"/>
-      <c r="AW42" s="13"/>
+          <t>FBM</t>
+        </is>
+      </c>
+      <c r="AU42" s="13" t="inlineStr">
+        <is>
+          <t>CN(HK)</t>
+        </is>
+      </c>
+      <c r="AV42" s="14" t="inlineStr">
+        <is>
+          <t>KWAI CHUNG HONG KONG 999077 HK</t>
+        </is>
+      </c>
+      <c r="AW42" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A23Q7Y7QJIMLUB</t>
+        </is>
+      </c>
       <c r="AX42" s="13"/>
       <c r="AY42" s="13"/>
       <c r="AZ42" s="13"/>
       <c r="BA42" s="13"/>
       <c r="BB42" s="13"/>
-      <c r="BC42" s="13"/>
-      <c r="BD42" s="13"/>
+      <c r="BC42" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD42" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE42" s="13"/>
       <c r="BF42" s="13"/>
       <c r="BG42" s="13"/>
       <c r="BH42" s="14"/>
       <c r="BI42" s="23"/>
-      <c r="BJ42" s="23" t="inlineStr">
-        <is>
-          <t>2,69 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK42" s="23" t="inlineStr">
-        <is>
-          <t>2.69 kg</t>
-        </is>
-      </c>
+      <c r="BJ42" s="23"/>
+      <c r="BK42" s="23"/>
       <c r="BL42" s="23" t="inlineStr">
         <is>
-          <t>29,5L x 22l x 18,2H centimètres</t>
+          <t>17L x 35,5l x 25H centimètres</t>
         </is>
       </c>
       <c r="BM42" s="23"/>
@@ -14115,69 +14147,53 @@
       <c r="B43" s="13"/>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>B0HFSKFZVX</t>
+          <t>B0HG94VY37</t>
         </is>
       </c>
       <c r="D43" s="14"/>
       <c r="E43" s="14"/>
       <c r="F43" s="14" t="inlineStr">
         <is>
-          <t>IERAKOR</t>
+          <t>NIPOO</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=IERAKOR</t>
+          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=NIPOO</t>
         </is>
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>IERAKOR Aspirateur Matelas Anti Acariens avec Lumière UV, 16kPa Aspirations600W Aspirateur à Main, Air Chaud 140°F, ultraso</t>
+          <t>NIPOO Aspirateur anti-acariens pour matelas, 500 W, aspirateur de lit avec lumière UV, filtre HEPA, fonction air chaud, capte</t>
         </is>
       </c>
       <c r="I43" s="14"/>
       <c r="J43" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0HFSKFZVX?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0HG94VY37?psc=1</t>
         </is>
       </c>
       <c r="K43" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71XDAjt0gLL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41UZPPhAkfL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L43" s="14" t="inlineStr">
         <is>
-          <t>B0HFSKFZVX</t>
+          <t>B0HG94VY37</t>
         </is>
       </c>
       <c r="M43" s="14" t="inlineStr">
         <is>
-          <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Aspirateurs:Aspirateurs à main</t>
-        </is>
-      </c>
-      <c r="N43" s="14" t="inlineStr">
-        <is>
-          <t>Voir les 100 premiers en Cuisine et Maison</t>
-        </is>
-      </c>
-      <c r="O43" s="15">
-        <v>371717</v>
-      </c>
+          <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Aspirateurs:Aspirateurs pour futons</t>
+        </is>
+      </c>
+      <c r="N43" s="14"/>
+      <c r="O43" s="15"/>
       <c r="P43" s="15"/>
-      <c r="Q43" s="16">
-        <v>0</v>
-      </c>
-      <c r="R43" s="17" t="inlineStr">
-        <is>
-          <t>Aspirateurs à main</t>
-        </is>
-      </c>
-      <c r="S43" s="18" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
+      <c r="Q43" s="16"/>
+      <c r="R43" s="17"/>
+      <c r="S43" s="18"/>
       <c r="T43" s="15"/>
       <c r="U43" s="16"/>
       <c r="V43" s="15"/>
@@ -14192,68 +14208,54 @@
       <c r="AA43"/>
       <c r="AB43"/>
       <c r="AC43" s="2"/>
-      <c r="AD43" s="19">
-        <v>8</v>
-      </c>
+      <c r="AD43" s="19"/>
       <c r="AE43" s="15">
-        <v>2</v>
-      </c>
-      <c r="AF43" s="21">
-        <v>5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF43" s="21"/>
       <c r="AG43" s="22">
         <v>0</v>
       </c>
       <c r="AH43" s="20"/>
       <c r="AI43" s="16">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="AJ43"/>
       <c r="AK43" s="13" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AL43" s="19">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="AM43" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN43" s="13"/>
       <c r="AO43" s="13"/>
       <c r="AP43"/>
-      <c r="AQ43" s="19">
-        <v>9</v>
-      </c>
+      <c r="AQ43" s="19"/>
       <c r="AR43" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS43" s="14" t="inlineStr">
         <is>
-          <t>aijuzhang_01</t>
+          <t>Heruyan</t>
         </is>
       </c>
       <c r="AT43" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
-        </is>
-      </c>
-      <c r="AU43" s="13" t="inlineStr">
-        <is>
-          <t>CN(HK)</t>
-        </is>
-      </c>
-      <c r="AV43" s="14" t="inlineStr">
-        <is>
-          <t>KWAI CHUNG HONG KONG 999077 HK</t>
-        </is>
-      </c>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="AU43" s="13"/>
+      <c r="AV43" s="14"/>
       <c r="AW43" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A23Q7Y7QJIMLUB</t>
+          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2SJ2YMMRH9IM6</t>
         </is>
       </c>
       <c r="AX43" s="13"/>
@@ -14261,26 +14263,26 @@
       <c r="AZ43" s="13"/>
       <c r="BA43" s="13"/>
       <c r="BB43" s="13"/>
-      <c r="BC43" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD43" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC43" s="13"/>
+      <c r="BD43" s="13"/>
       <c r="BE43" s="13"/>
       <c r="BF43" s="13"/>
       <c r="BG43" s="13"/>
       <c r="BH43" s="14"/>
       <c r="BI43" s="23"/>
-      <c r="BJ43" s="23"/>
-      <c r="BK43" s="23"/>
+      <c r="BJ43" s="23" t="inlineStr">
+        <is>
+          <t>1,44 Kilograms</t>
+        </is>
+      </c>
+      <c r="BK43" s="23" t="inlineStr">
+        <is>
+          <t>1.44 kg</t>
+        </is>
+      </c>
       <c r="BL43" s="23" t="inlineStr">
         <is>
-          <t>17L x 35,5l x 25H centimètres</t>
+          <t>26,9L x 24,9l x 14H centimètres</t>
         </is>
       </c>
       <c r="BM43" s="23"/>
@@ -14289,158 +14291,6 @@
       <c r="BP43" s="23"/>
       <c r="BQ43" s="23"/>
       <c r="BR43" s="13"/>
-    </row>
-    <row r="44" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="13">
-        <v>43</v>
-      </c>
-      <c r="B44" s="13"/>
-      <c r="C44" s="14" t="inlineStr">
-        <is>
-          <t>B0HG94VY37</t>
-        </is>
-      </c>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14" t="inlineStr">
-        <is>
-          <t>NIPOO</t>
-        </is>
-      </c>
-      <c r="G44" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=NIPOO</t>
-        </is>
-      </c>
-      <c r="H44" s="14" t="inlineStr">
-        <is>
-          <t>NIPOO Aspirateur anti-acariens pour matelas, 500 W, aspirateur de lit avec lumière UV, filtre HEPA, fonction air chaud, capte</t>
-        </is>
-      </c>
-      <c r="I44" s="14"/>
-      <c r="J44" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/dp/B0HG94VY37?psc=1</t>
-        </is>
-      </c>
-      <c r="K44" s="14" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/41UZPPhAkfL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L44" s="14" t="inlineStr">
-        <is>
-          <t>B0HG94VY37</t>
-        </is>
-      </c>
-      <c r="M44" s="14" t="inlineStr">
-        <is>
-          <t>Cuisine et Maison:Aspirateurs, entretien des sols et nettoyeurs de vitres:Aspirateurs:Aspirateurs pour futons</t>
-        </is>
-      </c>
-      <c r="N44" s="14"/>
-      <c r="O44" s="15"/>
-      <c r="P44" s="15"/>
-      <c r="Q44" s="16"/>
-      <c r="R44" s="17"/>
-      <c r="S44" s="18"/>
-      <c r="T44" s="15"/>
-      <c r="U44" s="16"/>
-      <c r="V44" s="15"/>
-      <c r="W44" s="15"/>
-      <c r="X44" s="15"/>
-      <c r="Y44" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z44" s="20">
-        <v>89.99</v>
-      </c>
-      <c r="AA44"/>
-      <c r="AB44"/>
-      <c r="AC44" s="2"/>
-      <c r="AD44" s="19"/>
-      <c r="AE44" s="15">
-        <v>0</v>
-      </c>
-      <c r="AF44" s="21"/>
-      <c r="AG44" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH44" s="20"/>
-      <c r="AI44" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ44"/>
-      <c r="AK44" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AL44" s="19">
-        <v>27</v>
-      </c>
-      <c r="AM44" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AN44" s="13"/>
-      <c r="AO44" s="13"/>
-      <c r="AP44"/>
-      <c r="AQ44" s="19"/>
-      <c r="AR44" s="19">
-        <v>2</v>
-      </c>
-      <c r="AS44" s="14" t="inlineStr">
-        <is>
-          <t>Heruyan</t>
-        </is>
-      </c>
-      <c r="AT44" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU44" s="13"/>
-      <c r="AV44" s="14"/>
-      <c r="AW44" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2SJ2YMMRH9IM6</t>
-        </is>
-      </c>
-      <c r="AX44" s="13"/>
-      <c r="AY44" s="13"/>
-      <c r="AZ44" s="13"/>
-      <c r="BA44" s="13"/>
-      <c r="BB44" s="13"/>
-      <c r="BC44" s="13"/>
-      <c r="BD44" s="13"/>
-      <c r="BE44" s="13"/>
-      <c r="BF44" s="13"/>
-      <c r="BG44" s="13"/>
-      <c r="BH44" s="14"/>
-      <c r="BI44" s="23"/>
-      <c r="BJ44" s="23" t="inlineStr">
-        <is>
-          <t>1,44 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK44" s="23" t="inlineStr">
-        <is>
-          <t>1.44 kg</t>
-        </is>
-      </c>
-      <c r="BL44" s="23" t="inlineStr">
-        <is>
-          <t>26,9L x 24,9l x 14H centimètres</t>
-        </is>
-      </c>
-      <c r="BM44" s="23"/>
-      <c r="BN44" s="23"/>
-      <c r="BO44" s="23"/>
-      <c r="BP44" s="23"/>
-      <c r="BQ44" s="23"/>
-      <c r="BR44" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14617,150 +14467,145 @@
     <hyperlink ref="M23" r:id="rId169" tooltip="https://www.amazon.fr/b?node=13519663031"/>
     <hyperlink ref="N23" r:id="rId170"/>
     <hyperlink ref="AW23" r:id="rId171" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A144XIL10CDODF"/>
-    <hyperlink ref="C24" r:id="rId172" tooltip="https://www.amazon.fr/dp/B0DWJQ9GFY"/>
-    <hyperlink ref="G24" r:id="rId173" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J24" r:id="rId174" tooltip="https://www.amazon.fr/dp/B0DWJQ9GFY?psc=1"/>
-    <hyperlink ref="K24" r:id="rId175" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61bbwwWUftL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L24" r:id="rId176" tooltip="https://www.amazon.fr/dp/B0DWJQ9GFY"/>
-    <hyperlink ref="C25" r:id="rId177" tooltip="https://www.amazon.fr/dp/B0F6MX5L26"/>
-    <hyperlink ref="G25" r:id="rId178" tooltip="https://www.amazon.fr/stores/JIGOO-FR/page/17D55FBF-0728-4B52-B93A-38FB4976CB6E?lp_asin=B0F6MX5L26&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J25" r:id="rId179" tooltip="https://www.amazon.fr/dp/B0F6MX5L26?psc=1"/>
-    <hyperlink ref="K25" r:id="rId180" tooltip="https://images-na.ssl-images-amazon.com/images/I/71zSxKlDt9L._AC_US600_.jpg"/>
-    <hyperlink ref="L25" r:id="rId181" tooltip="https://www.amazon.fr/dp/B0F6MX5L26"/>
-    <hyperlink ref="M25" r:id="rId182" tooltip="https://www.amazon.fr/b?node=13519663031"/>
-    <hyperlink ref="N25" r:id="rId183"/>
-    <hyperlink ref="AW25" r:id="rId184" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3UYKG1D6EID1Q"/>
-    <hyperlink ref="C26" r:id="rId185" tooltip="https://www.amazon.fr/dp/B0F6XNKG8M"/>
-    <hyperlink ref="G26" r:id="rId186" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J26" r:id="rId187" tooltip="https://www.amazon.fr/dp/B0F6XNKG8M?psc=1"/>
-    <hyperlink ref="K26" r:id="rId188" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71iADJb-ECL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L26" r:id="rId189" tooltip="https://www.amazon.fr/dp/B0F6XNKG8M"/>
-    <hyperlink ref="C27" r:id="rId190" tooltip="https://www.amazon.fr/dp/B0F9NJM4V9"/>
-    <hyperlink ref="G27" r:id="rId191" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Liwankaqi"/>
-    <hyperlink ref="J27" r:id="rId192" tooltip="https://www.amazon.fr/dp/B0F9NJM4V9?psc=1"/>
-    <hyperlink ref="K27" r:id="rId193" tooltip="https://images-na.ssl-images-amazon.com/images/I/61GdOBS8v+L._AC_US600_.jpg"/>
-    <hyperlink ref="L27" r:id="rId194" tooltip="https://www.amazon.fr/dp/B0F9NJM4V9"/>
-    <hyperlink ref="M27" r:id="rId195" tooltip="https://www.amazon.fr/b?node=13519663031"/>
-    <hyperlink ref="N27" r:id="rId196"/>
-    <hyperlink ref="AW27" r:id="rId197" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1CO438NU9H9Y"/>
-    <hyperlink ref="C28" r:id="rId198" tooltip="https://www.amazon.fr/dp/B0FDWVV95V"/>
-    <hyperlink ref="G28" r:id="rId199" tooltip="https://www.amazon.fr/stores/JIGOO-FR/page/17D55FBF-0728-4B52-B93A-38FB4976CB6E?lp_asin=B0FDWVV95V&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J28" r:id="rId200" tooltip="https://www.amazon.fr/dp/B0FDWVV95V?psc=1"/>
-    <hyperlink ref="K28" r:id="rId201" tooltip="https://images-na.ssl-images-amazon.com/images/I/61tL+-AcL6L._AC_US600_.jpg"/>
-    <hyperlink ref="L28" r:id="rId202" tooltip="https://www.amazon.fr/dp/B0FDWVV95V"/>
-    <hyperlink ref="M28" r:id="rId203" tooltip="https://www.amazon.fr/b?node=13519663031"/>
-    <hyperlink ref="N28" r:id="rId204"/>
-    <hyperlink ref="AW28" r:id="rId205" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1OG68CATOOAOD"/>
-    <hyperlink ref="C29" r:id="rId206" tooltip="https://www.amazon.fr/dp/B0FN3V6RFQ"/>
-    <hyperlink ref="G29" r:id="rId207" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J29" r:id="rId208" tooltip="https://www.amazon.fr/dp/B0FN3V6RFQ?psc=1"/>
-    <hyperlink ref="K29" r:id="rId209" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71YynWtKuIL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L29" r:id="rId210" tooltip="https://www.amazon.fr/dp/B0FN3V6RFQ"/>
-    <hyperlink ref="C30" r:id="rId211" tooltip="https://www.amazon.fr/dp/B0FVS559GZ"/>
-    <hyperlink ref="G30" r:id="rId212" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier"/>
-    <hyperlink ref="J30" r:id="rId213" tooltip="https://www.amazon.fr/dp/B0FVS559GZ?psc=1"/>
-    <hyperlink ref="K30" r:id="rId214" tooltip="https://m.media-amazon.com/images/I/31eLjeocEiL._AC_US600_.jpg"/>
-    <hyperlink ref="L30" r:id="rId215" tooltip="https://www.amazon.fr/dp/B0FVS559GZ"/>
-    <hyperlink ref="M30" r:id="rId216" tooltip="https://www.amazon.fr/b?node=13519663031"/>
-    <hyperlink ref="N30" r:id="rId217"/>
-    <hyperlink ref="AW30" r:id="rId218" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX"/>
-    <hyperlink ref="C31" r:id="rId219" tooltip="https://www.amazon.fr/dp/B0FYM1D13D"/>
-    <hyperlink ref="G31" r:id="rId220" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J31" r:id="rId221" tooltip="https://www.amazon.fr/dp/B0FYM1D13D?psc=1"/>
-    <hyperlink ref="K31" r:id="rId222" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L31" r:id="rId223" tooltip="https://www.amazon.fr/dp/B0FYM1D13D"/>
-    <hyperlink ref="C32" r:id="rId224" tooltip="https://www.amazon.fr/dp/B0G4RSJQVT"/>
-    <hyperlink ref="G32" r:id="rId225" tooltip="https://www.amazon.fr/stores/Lubluelu/page/C74A1C3B-E92E-40F7-8500-E72C2F4BD6F3?lp_asin=B0G4RSJQVT&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J32" r:id="rId226" tooltip="https://www.amazon.fr/dp/B0G4RSJQVT?psc=1"/>
-    <hyperlink ref="K32" r:id="rId227" tooltip="https://m.media-amazon.com/images/I/41T59G+lWKL._AC_US600_.jpg"/>
-    <hyperlink ref="L32" r:id="rId228" tooltip="https://www.amazon.fr/dp/B0G4RSJQVT"/>
-    <hyperlink ref="M32" r:id="rId229" tooltip="https://www.amazon.fr/b?node=13519663031"/>
-    <hyperlink ref="N32" r:id="rId230"/>
-    <hyperlink ref="AW32" r:id="rId231" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A23BRZJD26C30N"/>
-    <hyperlink ref="C33" r:id="rId232" tooltip="https://www.amazon.fr/dp/B0GF7CNTYL"/>
-    <hyperlink ref="G33" r:id="rId233" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Liwankaqi"/>
-    <hyperlink ref="J33" r:id="rId234" tooltip="https://www.amazon.fr/dp/B0GF7CNTYL?psc=1"/>
-    <hyperlink ref="K33" r:id="rId235" tooltip="https://images-na.ssl-images-amazon.com/images/I/71H9bRmoUnL._AC_US600_.jpg"/>
-    <hyperlink ref="L33" r:id="rId236" tooltip="https://www.amazon.fr/dp/B0GF7CNTYL"/>
-    <hyperlink ref="M33" r:id="rId237" tooltip="https://www.amazon.fr/b?node=13519663031"/>
-    <hyperlink ref="N33" r:id="rId238"/>
-    <hyperlink ref="AW33" r:id="rId239" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1CO438NU9H9Y"/>
-    <hyperlink ref="C34" r:id="rId240" tooltip="https://www.amazon.fr/dp/B0GGBLWNRZ"/>
+    <hyperlink ref="C24" r:id="rId172" tooltip="https://www.amazon.fr/dp/B0F6MX5L26"/>
+    <hyperlink ref="G24" r:id="rId173" tooltip="https://www.amazon.fr/stores/JIGOO-FR/page/17D55FBF-0728-4B52-B93A-38FB4976CB6E?lp_asin=B0F6MX5L26&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J24" r:id="rId174" tooltip="https://www.amazon.fr/dp/B0F6MX5L26?psc=1"/>
+    <hyperlink ref="K24" r:id="rId175" tooltip="https://images-na.ssl-images-amazon.com/images/I/71zSxKlDt9L._AC_US600_.jpg"/>
+    <hyperlink ref="L24" r:id="rId176" tooltip="https://www.amazon.fr/dp/B0F6MX5L26"/>
+    <hyperlink ref="M24" r:id="rId177" tooltip="https://www.amazon.fr/b?node=13519663031"/>
+    <hyperlink ref="N24" r:id="rId178"/>
+    <hyperlink ref="AW24" r:id="rId179" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3UYKG1D6EID1Q"/>
+    <hyperlink ref="C25" r:id="rId180" tooltip="https://www.amazon.fr/dp/B0F6XNKG8M"/>
+    <hyperlink ref="G25" r:id="rId181" tooltip="https://www.amazon.frundefined"/>
+    <hyperlink ref="J25" r:id="rId182" tooltip="https://www.amazon.fr/dp/B0F6XNKG8M?psc=1"/>
+    <hyperlink ref="K25" r:id="rId183" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71iADJb-ECL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L25" r:id="rId184" tooltip="https://www.amazon.fr/dp/B0F6XNKG8M"/>
+    <hyperlink ref="C26" r:id="rId185" tooltip="https://www.amazon.fr/dp/B0F9NJM4V9"/>
+    <hyperlink ref="G26" r:id="rId186" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Liwankaqi"/>
+    <hyperlink ref="J26" r:id="rId187" tooltip="https://www.amazon.fr/dp/B0F9NJM4V9?psc=1"/>
+    <hyperlink ref="K26" r:id="rId188" tooltip="https://images-na.ssl-images-amazon.com/images/I/61GdOBS8v+L._AC_US600_.jpg"/>
+    <hyperlink ref="L26" r:id="rId189" tooltip="https://www.amazon.fr/dp/B0F9NJM4V9"/>
+    <hyperlink ref="M26" r:id="rId190" tooltip="https://www.amazon.fr/b?node=13519663031"/>
+    <hyperlink ref="N26" r:id="rId191"/>
+    <hyperlink ref="AW26" r:id="rId192" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1CO438NU9H9Y"/>
+    <hyperlink ref="C27" r:id="rId193" tooltip="https://www.amazon.fr/dp/B0FDWVV95V"/>
+    <hyperlink ref="G27" r:id="rId194" tooltip="https://www.amazon.fr/stores/JIGOO-FR/page/17D55FBF-0728-4B52-B93A-38FB4976CB6E?lp_asin=B0FDWVV95V&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J27" r:id="rId195" tooltip="https://www.amazon.fr/dp/B0FDWVV95V?psc=1"/>
+    <hyperlink ref="K27" r:id="rId196" tooltip="https://images-na.ssl-images-amazon.com/images/I/61tL+-AcL6L._AC_US600_.jpg"/>
+    <hyperlink ref="L27" r:id="rId197" tooltip="https://www.amazon.fr/dp/B0FDWVV95V"/>
+    <hyperlink ref="M27" r:id="rId198" tooltip="https://www.amazon.fr/b?node=13519663031"/>
+    <hyperlink ref="N27" r:id="rId199"/>
+    <hyperlink ref="AW27" r:id="rId200" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1OG68CATOOAOD"/>
+    <hyperlink ref="C28" r:id="rId201" tooltip="https://www.amazon.fr/dp/B0FN3V6RFQ"/>
+    <hyperlink ref="G28" r:id="rId202" tooltip="https://www.amazon.frundefined"/>
+    <hyperlink ref="J28" r:id="rId203" tooltip="https://www.amazon.fr/dp/B0FN3V6RFQ?psc=1"/>
+    <hyperlink ref="K28" r:id="rId204" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71YynWtKuIL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L28" r:id="rId205" tooltip="https://www.amazon.fr/dp/B0FN3V6RFQ"/>
+    <hyperlink ref="C29" r:id="rId206" tooltip="https://www.amazon.fr/dp/B0FVS559GZ"/>
+    <hyperlink ref="G29" r:id="rId207" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Yaasier"/>
+    <hyperlink ref="J29" r:id="rId208" tooltip="https://www.amazon.fr/dp/B0FVS559GZ?psc=1"/>
+    <hyperlink ref="K29" r:id="rId209" tooltip="https://m.media-amazon.com/images/I/31eLjeocEiL._AC_US600_.jpg"/>
+    <hyperlink ref="L29" r:id="rId210" tooltip="https://www.amazon.fr/dp/B0FVS559GZ"/>
+    <hyperlink ref="M29" r:id="rId211" tooltip="https://www.amazon.fr/b?node=13519663031"/>
+    <hyperlink ref="N29" r:id="rId212"/>
+    <hyperlink ref="AW29" r:id="rId213" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ATK258MBI08TX"/>
+    <hyperlink ref="C30" r:id="rId214" tooltip="https://www.amazon.fr/dp/B0FYM1D13D"/>
+    <hyperlink ref="G30" r:id="rId215" tooltip="https://www.amazon.frundefined"/>
+    <hyperlink ref="J30" r:id="rId216" tooltip="https://www.amazon.fr/dp/B0FYM1D13D?psc=1"/>
+    <hyperlink ref="K30" r:id="rId217" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L30" r:id="rId218" tooltip="https://www.amazon.fr/dp/B0FYM1D13D"/>
+    <hyperlink ref="C31" r:id="rId219" tooltip="https://www.amazon.fr/dp/B0G4RSJQVT"/>
+    <hyperlink ref="G31" r:id="rId220" tooltip="https://www.amazon.fr/stores/Lubluelu/page/C74A1C3B-E92E-40F7-8500-E72C2F4BD6F3?lp_asin=B0G4RSJQVT&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J31" r:id="rId221" tooltip="https://www.amazon.fr/dp/B0G4RSJQVT?psc=1"/>
+    <hyperlink ref="K31" r:id="rId222" tooltip="https://m.media-amazon.com/images/I/41T59G+lWKL._AC_US600_.jpg"/>
+    <hyperlink ref="L31" r:id="rId223" tooltip="https://www.amazon.fr/dp/B0G4RSJQVT"/>
+    <hyperlink ref="M31" r:id="rId224" tooltip="https://www.amazon.fr/b?node=13519663031"/>
+    <hyperlink ref="N31" r:id="rId225"/>
+    <hyperlink ref="AW31" r:id="rId226" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A23BRZJD26C30N"/>
+    <hyperlink ref="C32" r:id="rId227" tooltip="https://www.amazon.fr/dp/B0GF7CNTYL"/>
+    <hyperlink ref="G32" r:id="rId228" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Liwankaqi"/>
+    <hyperlink ref="J32" r:id="rId229" tooltip="https://www.amazon.fr/dp/B0GF7CNTYL?psc=1"/>
+    <hyperlink ref="K32" r:id="rId230" tooltip="https://images-na.ssl-images-amazon.com/images/I/71H9bRmoUnL._AC_US600_.jpg"/>
+    <hyperlink ref="L32" r:id="rId231" tooltip="https://www.amazon.fr/dp/B0GF7CNTYL"/>
+    <hyperlink ref="M32" r:id="rId232" tooltip="https://www.amazon.fr/b?node=13519663031"/>
+    <hyperlink ref="N32" r:id="rId233"/>
+    <hyperlink ref="AW32" r:id="rId234" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1CO438NU9H9Y"/>
+    <hyperlink ref="C33" r:id="rId235" tooltip="https://www.amazon.fr/dp/B0GGBLWNRZ"/>
+    <hyperlink ref="G33" r:id="rId236" tooltip="https://www.amazon.frundefined"/>
+    <hyperlink ref="J33" r:id="rId237" tooltip="https://www.amazon.fr/dp/B0GGBLWNRZ?psc=1"/>
+    <hyperlink ref="K33" r:id="rId238" tooltip="https://images-eu.ssl-images-amazon.com/images/I/41xNIs1B-1L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L33" r:id="rId239" tooltip="https://www.amazon.fr/dp/B0GGBLWNRZ"/>
+    <hyperlink ref="C34" r:id="rId240" tooltip="https://www.amazon.fr/dp/B0GMPVWCZM"/>
     <hyperlink ref="G34" r:id="rId241" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J34" r:id="rId242" tooltip="https://www.amazon.fr/dp/B0GGBLWNRZ?psc=1"/>
-    <hyperlink ref="K34" r:id="rId243" tooltip="https://images-eu.ssl-images-amazon.com/images/I/41xNIs1B-1L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L34" r:id="rId244" tooltip="https://www.amazon.fr/dp/B0GGBLWNRZ"/>
-    <hyperlink ref="C35" r:id="rId245" tooltip="https://www.amazon.fr/dp/B0GMPVWCZM"/>
-    <hyperlink ref="G35" r:id="rId246" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J35" r:id="rId247" tooltip="https://www.amazon.fr/dp/B0GMPVWCZM?psc=1"/>
-    <hyperlink ref="K35" r:id="rId248" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81J2yw2XZnL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L35" r:id="rId249" tooltip="https://www.amazon.fr/dp/B0GMPVWCZM"/>
-    <hyperlink ref="C36" r:id="rId250" tooltip="https://www.amazon.fr/dp/B0GT17NK5X"/>
-    <hyperlink ref="G36" r:id="rId251" tooltip="https://www.amazon.fr/XINYUDAILY/b/ref=bl_dp_s_web_85011884031?ie=UTF8&amp;node=85011884031&amp;field-lbr_brands_browse-bin=XINYUDAILY"/>
-    <hyperlink ref="J36" r:id="rId252" tooltip="https://www.amazon.fr/dp/B0GT17NK5X?psc=1"/>
-    <hyperlink ref="K36" r:id="rId253" tooltip="https://images-na.ssl-images-amazon.com/images/I/71ZkgBFQnaL._AC_US600_.jpg"/>
-    <hyperlink ref="L36" r:id="rId254" tooltip="https://www.amazon.fr/dp/B0GT17NK5X"/>
-    <hyperlink ref="M36" r:id="rId255" tooltip="https://www.amazon.fr/b?node=13519663031"/>
-    <hyperlink ref="N36" r:id="rId256"/>
-    <hyperlink ref="AW36" r:id="rId257" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AD38JSQ91A5LY"/>
-    <hyperlink ref="C37" r:id="rId258" tooltip="https://www.amazon.fr/dp/B0GWH1FGJB"/>
-    <hyperlink ref="G37" r:id="rId259" tooltip="https://www.amazon.fr/Timisea/b/ref=bl_dp_s_web_93230377031?ie=UTF8&amp;node=93230377031&amp;field-lbr_brands_browse-bin=Timisea"/>
-    <hyperlink ref="J37" r:id="rId260" tooltip="https://www.amazon.fr/dp/B0GWH1FGJB?psc=1"/>
-    <hyperlink ref="K37" r:id="rId261" tooltip="https://m.media-amazon.com/images/I/31txErJ7TmL._AC_US600_.jpg"/>
-    <hyperlink ref="L37" r:id="rId262" tooltip="https://www.amazon.fr/dp/B0GWH1FGJB"/>
-    <hyperlink ref="M37" r:id="rId263" tooltip="https://www.amazon.fr/b?node=13519663031"/>
-    <hyperlink ref="N37" r:id="rId264"/>
-    <hyperlink ref="AW37" r:id="rId265" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3SPQY2QF85KOQ"/>
-    <hyperlink ref="C38" r:id="rId266" tooltip="https://www.amazon.fr/dp/B0GYS43G8G"/>
-    <hyperlink ref="G38" r:id="rId267" tooltip="https://www.amazon.fr/stores/ALLILUYAA/page/B6AAB331-17D2-444A-B3E5-494EC94DE846?lp_asin=B0GYS43G8G&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J38" r:id="rId268" tooltip="https://www.amazon.fr/dp/B0GYS43G8G?psc=1"/>
-    <hyperlink ref="K38" r:id="rId269" tooltip="https://images-na.ssl-images-amazon.com/images/I/51JXrvAAoZL._AC_US600_.jpg"/>
-    <hyperlink ref="L38" r:id="rId270" tooltip="https://www.amazon.fr/dp/B0GYS43G8G"/>
-    <hyperlink ref="M38" r:id="rId271" tooltip="https://www.amazon.fr/b?node=13519663031"/>
-    <hyperlink ref="N38" r:id="rId272"/>
-    <hyperlink ref="AW38" r:id="rId273" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A238ODZG8O3E58"/>
-    <hyperlink ref="C39" r:id="rId274" tooltip="https://www.amazon.fr/dp/B0H6F2NPXK"/>
-    <hyperlink ref="G39" r:id="rId275" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J39" r:id="rId276" tooltip="https://www.amazon.fr/dp/B0H6F2NPXK?psc=1"/>
-    <hyperlink ref="K39" r:id="rId277" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61InrYvl2-L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L39" r:id="rId278" tooltip="https://www.amazon.fr/dp/B0H6F2NPXK"/>
-    <hyperlink ref="C40" r:id="rId279" tooltip="https://www.amazon.fr/dp/B0H712ZM35"/>
-    <hyperlink ref="G40" r:id="rId280" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Resmafn"/>
-    <hyperlink ref="J40" r:id="rId281" tooltip="https://www.amazon.fr/dp/B0H712ZM35?psc=1"/>
-    <hyperlink ref="K40" r:id="rId282" tooltip="https://m.media-amazon.com/images/I/41lzTiHI9yL._AC_US600_.jpg"/>
-    <hyperlink ref="L40" r:id="rId283" tooltip="https://www.amazon.fr/dp/B0H712ZM35"/>
-    <hyperlink ref="M40" r:id="rId284" tooltip="https://www.amazon.fr/b?node=13519663031"/>
-    <hyperlink ref="AW40" r:id="rId285" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3SB2QKWYM7MS5"/>
-    <hyperlink ref="C41" r:id="rId286" tooltip="https://www.amazon.fr/dp/B0H8XNCYS3"/>
-    <hyperlink ref="G41" r:id="rId287" tooltip="https://www.amazon.fr/Umllpet/b/ref=bl_dp_s_web_66106680031?ie=UTF8&amp;node=66106680031&amp;field-lbr_brands_browse-bin=Umllpet"/>
-    <hyperlink ref="J41" r:id="rId288" tooltip="https://www.amazon.fr/dp/B0H8XNCYS3?psc=1"/>
-    <hyperlink ref="K41" r:id="rId289" tooltip="https://m.media-amazon.com/images/I/412ayO2+-bL._AC_US600_.jpg"/>
-    <hyperlink ref="L41" r:id="rId290" tooltip="https://www.amazon.fr/dp/B0H8XNCYS3"/>
-    <hyperlink ref="M41" r:id="rId291" tooltip="https://www.amazon.fr/b?node=13519663031"/>
-    <hyperlink ref="AW41" r:id="rId292" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A5NA8IRE5E804"/>
-    <hyperlink ref="C42" r:id="rId293" tooltip="https://www.amazon.fr/dp/B0H984GBDC"/>
-    <hyperlink ref="G42" r:id="rId294" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Xlife"/>
-    <hyperlink ref="J42" r:id="rId295" tooltip="https://www.amazon.fr/dp/B0H984GBDC?psc=1"/>
-    <hyperlink ref="K42" r:id="rId296" tooltip="https://m.media-amazon.com/images/I/515qVEbm90L._AC_US600_.jpg"/>
-    <hyperlink ref="L42" r:id="rId297" tooltip="https://www.amazon.fr/dp/B0H984GBDC"/>
-    <hyperlink ref="M42" r:id="rId298" tooltip="https://www.amazon.fr/b?node=13519663031"/>
-    <hyperlink ref="C43" r:id="rId299" tooltip="https://www.amazon.fr/dp/B0HFSKFZVX"/>
-    <hyperlink ref="G43" r:id="rId300" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=IERAKOR"/>
-    <hyperlink ref="J43" r:id="rId301" tooltip="https://www.amazon.fr/dp/B0HFSKFZVX?psc=1"/>
-    <hyperlink ref="K43" r:id="rId302" tooltip="https://images-na.ssl-images-amazon.com/images/I/71XDAjt0gLL._AC_US600_.jpg"/>
-    <hyperlink ref="L43" r:id="rId303" tooltip="https://www.amazon.fr/dp/B0HFSKFZVX"/>
-    <hyperlink ref="M43" r:id="rId304" tooltip="https://www.amazon.fr/b?node=3575228031"/>
-    <hyperlink ref="N43" r:id="rId305"/>
-    <hyperlink ref="AW43" r:id="rId306" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A23Q7Y7QJIMLUB"/>
-    <hyperlink ref="C44" r:id="rId307" tooltip="https://www.amazon.fr/dp/B0HG94VY37"/>
-    <hyperlink ref="G44" r:id="rId308" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=NIPOO"/>
-    <hyperlink ref="J44" r:id="rId309" tooltip="https://www.amazon.fr/dp/B0HG94VY37?psc=1"/>
-    <hyperlink ref="K44" r:id="rId310" tooltip="https://m.media-amazon.com/images/I/41UZPPhAkfL._AC_US600_.jpg"/>
-    <hyperlink ref="L44" r:id="rId311" tooltip="https://www.amazon.fr/dp/B0HG94VY37"/>
-    <hyperlink ref="M44" r:id="rId312" tooltip="https://www.amazon.fr/b?node=13519663031"/>
-    <hyperlink ref="AW44" r:id="rId313" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2SJ2YMMRH9IM6"/>
+    <hyperlink ref="J34" r:id="rId242" tooltip="https://www.amazon.fr/dp/B0GMPVWCZM?psc=1"/>
+    <hyperlink ref="K34" r:id="rId243" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81J2yw2XZnL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L34" r:id="rId244" tooltip="https://www.amazon.fr/dp/B0GMPVWCZM"/>
+    <hyperlink ref="C35" r:id="rId245" tooltip="https://www.amazon.fr/dp/B0GT17NK5X"/>
+    <hyperlink ref="G35" r:id="rId246" tooltip="https://www.amazon.fr/XINYUDAILY/b/ref=bl_dp_s_web_85011884031?ie=UTF8&amp;node=85011884031&amp;field-lbr_brands_browse-bin=XINYUDAILY"/>
+    <hyperlink ref="J35" r:id="rId247" tooltip="https://www.amazon.fr/dp/B0GT17NK5X?psc=1"/>
+    <hyperlink ref="K35" r:id="rId248" tooltip="https://images-na.ssl-images-amazon.com/images/I/71ZkgBFQnaL._AC_US600_.jpg"/>
+    <hyperlink ref="L35" r:id="rId249" tooltip="https://www.amazon.fr/dp/B0GT17NK5X"/>
+    <hyperlink ref="M35" r:id="rId250" tooltip="https://www.amazon.fr/b?node=13519663031"/>
+    <hyperlink ref="N35" r:id="rId251"/>
+    <hyperlink ref="AW35" r:id="rId252" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AD38JSQ91A5LY"/>
+    <hyperlink ref="C36" r:id="rId253" tooltip="https://www.amazon.fr/dp/B0GWH1FGJB"/>
+    <hyperlink ref="G36" r:id="rId254" tooltip="https://www.amazon.fr/Timisea/b/ref=bl_dp_s_web_93230377031?ie=UTF8&amp;node=93230377031&amp;field-lbr_brands_browse-bin=Timisea"/>
+    <hyperlink ref="J36" r:id="rId255" tooltip="https://www.amazon.fr/dp/B0GWH1FGJB?psc=1"/>
+    <hyperlink ref="K36" r:id="rId256" tooltip="https://m.media-amazon.com/images/I/31txErJ7TmL._AC_US600_.jpg"/>
+    <hyperlink ref="L36" r:id="rId257" tooltip="https://www.amazon.fr/dp/B0GWH1FGJB"/>
+    <hyperlink ref="M36" r:id="rId258" tooltip="https://www.amazon.fr/b?node=13519663031"/>
+    <hyperlink ref="N36" r:id="rId259"/>
+    <hyperlink ref="AW36" r:id="rId260" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3SPQY2QF85KOQ"/>
+    <hyperlink ref="C37" r:id="rId261" tooltip="https://www.amazon.fr/dp/B0GYS43G8G"/>
+    <hyperlink ref="G37" r:id="rId262" tooltip="https://www.amazon.fr/stores/ALLILUYAA/page/B6AAB331-17D2-444A-B3E5-494EC94DE846?lp_asin=B0GYS43G8G&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J37" r:id="rId263" tooltip="https://www.amazon.fr/dp/B0GYS43G8G?psc=1"/>
+    <hyperlink ref="K37" r:id="rId264" tooltip="https://images-na.ssl-images-amazon.com/images/I/51JXrvAAoZL._AC_US600_.jpg"/>
+    <hyperlink ref="L37" r:id="rId265" tooltip="https://www.amazon.fr/dp/B0GYS43G8G"/>
+    <hyperlink ref="M37" r:id="rId266" tooltip="https://www.amazon.fr/b?node=13519663031"/>
+    <hyperlink ref="N37" r:id="rId267"/>
+    <hyperlink ref="AW37" r:id="rId268" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A238ODZG8O3E58"/>
+    <hyperlink ref="C38" r:id="rId269" tooltip="https://www.amazon.fr/dp/B0H6F2NPXK"/>
+    <hyperlink ref="G38" r:id="rId270" tooltip="https://www.amazon.frundefined"/>
+    <hyperlink ref="J38" r:id="rId271" tooltip="https://www.amazon.fr/dp/B0H6F2NPXK?psc=1"/>
+    <hyperlink ref="K38" r:id="rId272" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61InrYvl2-L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L38" r:id="rId273" tooltip="https://www.amazon.fr/dp/B0H6F2NPXK"/>
+    <hyperlink ref="C39" r:id="rId274" tooltip="https://www.amazon.fr/dp/B0H712ZM35"/>
+    <hyperlink ref="G39" r:id="rId275" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Resmafn"/>
+    <hyperlink ref="J39" r:id="rId276" tooltip="https://www.amazon.fr/dp/B0H712ZM35?psc=1"/>
+    <hyperlink ref="K39" r:id="rId277" tooltip="https://m.media-amazon.com/images/I/41lzTiHI9yL._AC_US600_.jpg"/>
+    <hyperlink ref="L39" r:id="rId278" tooltip="https://www.amazon.fr/dp/B0H712ZM35"/>
+    <hyperlink ref="M39" r:id="rId279" tooltip="https://www.amazon.fr/b?node=13519663031"/>
+    <hyperlink ref="AW39" r:id="rId280" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3SB2QKWYM7MS5"/>
+    <hyperlink ref="C40" r:id="rId281" tooltip="https://www.amazon.fr/dp/B0H8XNCYS3"/>
+    <hyperlink ref="G40" r:id="rId282" tooltip="https://www.amazon.fr/Umllpet/b/ref=bl_dp_s_web_66106680031?ie=UTF8&amp;node=66106680031&amp;field-lbr_brands_browse-bin=Umllpet"/>
+    <hyperlink ref="J40" r:id="rId283" tooltip="https://www.amazon.fr/dp/B0H8XNCYS3?psc=1"/>
+    <hyperlink ref="K40" r:id="rId284" tooltip="https://m.media-amazon.com/images/I/412ayO2+-bL._AC_US600_.jpg"/>
+    <hyperlink ref="L40" r:id="rId285" tooltip="https://www.amazon.fr/dp/B0H8XNCYS3"/>
+    <hyperlink ref="M40" r:id="rId286" tooltip="https://www.amazon.fr/b?node=13519663031"/>
+    <hyperlink ref="AW40" r:id="rId287" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A5NA8IRE5E804"/>
+    <hyperlink ref="C41" r:id="rId288" tooltip="https://www.amazon.fr/dp/B0H984GBDC"/>
+    <hyperlink ref="G41" r:id="rId289" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Xlife"/>
+    <hyperlink ref="J41" r:id="rId290" tooltip="https://www.amazon.fr/dp/B0H984GBDC?psc=1"/>
+    <hyperlink ref="K41" r:id="rId291" tooltip="https://m.media-amazon.com/images/I/515qVEbm90L._AC_US600_.jpg"/>
+    <hyperlink ref="L41" r:id="rId292" tooltip="https://www.amazon.fr/dp/B0H984GBDC"/>
+    <hyperlink ref="M41" r:id="rId293" tooltip="https://www.amazon.fr/b?node=13519663031"/>
+    <hyperlink ref="C42" r:id="rId294" tooltip="https://www.amazon.fr/dp/B0HFSKFZVX"/>
+    <hyperlink ref="G42" r:id="rId295" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=IERAKOR"/>
+    <hyperlink ref="J42" r:id="rId296" tooltip="https://www.amazon.fr/dp/B0HFSKFZVX?psc=1"/>
+    <hyperlink ref="K42" r:id="rId297" tooltip="https://images-na.ssl-images-amazon.com/images/I/71XDAjt0gLL._AC_US600_.jpg"/>
+    <hyperlink ref="L42" r:id="rId298" tooltip="https://www.amazon.fr/dp/B0HFSKFZVX"/>
+    <hyperlink ref="M42" r:id="rId299" tooltip="https://www.amazon.fr/b?node=3575228031"/>
+    <hyperlink ref="N42" r:id="rId300"/>
+    <hyperlink ref="AW42" r:id="rId301" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A23Q7Y7QJIMLUB"/>
+    <hyperlink ref="C43" r:id="rId302" tooltip="https://www.amazon.fr/dp/B0HG94VY37"/>
+    <hyperlink ref="G43" r:id="rId303" tooltip="https://www.amazon.fr/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=NIPOO"/>
+    <hyperlink ref="J43" r:id="rId304" tooltip="https://www.amazon.fr/dp/B0HG94VY37?psc=1"/>
+    <hyperlink ref="K43" r:id="rId305" tooltip="https://m.media-amazon.com/images/I/41UZPPhAkfL._AC_US600_.jpg"/>
+    <hyperlink ref="L43" r:id="rId306" tooltip="https://www.amazon.fr/dp/B0HG94VY37"/>
+    <hyperlink ref="M43" r:id="rId307" tooltip="https://www.amazon.fr/b?node=13519663031"/>
+    <hyperlink ref="AW43" r:id="rId308" tooltip="https://www.amazon.fr/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2SJ2YMMRH9IM6"/>
   </hyperlinks>
-  <drawing r:id="rId314"/>
+  <drawing r:id="rId309"/>
 </worksheet>
 </file>
 
